--- a/Day 2/DAY 2 SUMIF,IF,IFS.xlsx
+++ b/Day 2/DAY 2 SUMIF,IF,IFS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prince patel\Documents\prelytix-data_analytics\Day 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4666F34-E754-4B73-A905-AB4BF4CC1C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A2CC6C-742D-4F4F-B138-62ABC4B56E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{74D63399-A806-4BC2-B42A-1EC48C5562D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="96">
   <si>
     <t>Order_ID</t>
   </si>
@@ -729,6 +729,33 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -742,33 +769,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1465,6 +1465,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
@@ -1494,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C037ABF2-7B5D-42CA-A96E-A0DF32920A41}">
-  <dimension ref="A1:AC502"/>
+  <dimension ref="A1:AF502"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -1517,6 +1520,7 @@
     <col min="27" max="27" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1591,15 +1595,15 @@
       <c r="J2" s="17">
         <v>12648.46</v>
       </c>
-      <c r="K2" s="36" t="str">
+      <c r="K2" s="29" t="str">
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L2" s="37" t="str" cm="1">
+      <c r="L2" s="30" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M2" s="37" t="str" cm="1">
+      <c r="M2" s="30" t="str" cm="1">
         <f t="array" ref="M2">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -1639,11 +1643,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L3" s="37" t="str" cm="1">
+      <c r="L3" s="30" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M3" s="39" t="str" cm="1">
+      <c r="M3" s="32" t="str" cm="1">
         <f t="array" ref="M3">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -1683,22 +1687,22 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L4" s="37" t="str" cm="1">
+      <c r="L4" s="30" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M4" s="39" t="str" cm="1">
+      <c r="M4" s="32" t="str" cm="1">
         <f t="array" ref="M4">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="P4" s="34" t="s">
+      <c r="P4" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
@@ -1735,11 +1739,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L5" s="37" t="str" cm="1">
+      <c r="L5" s="30" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M5" s="39" t="str" cm="1">
+      <c r="M5" s="32" t="str" cm="1">
         <f t="array" ref="M5">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -1779,11 +1783,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L6" s="37" t="str" cm="1">
+      <c r="L6" s="30" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M6" s="39" t="str" cm="1">
+      <c r="M6" s="32" t="str" cm="1">
         <f t="array" ref="M6">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -1841,11 +1845,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L7" s="37" t="str" cm="1">
+      <c r="L7" s="30" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M7" s="39" t="str" cm="1">
+      <c r="M7" s="32" t="str" cm="1">
         <f t="array" ref="M7">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -1869,7 +1873,7 @@
         <f>COUNTIF(Table4[Product],"MOBILE")</f>
         <v>54</v>
       </c>
-      <c r="X7" s="46" t="s">
+      <c r="X7" s="37" t="s">
         <v>90</v>
       </c>
       <c r="Y7" t="s">
@@ -1911,11 +1915,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L8" s="37" t="str" cm="1">
+      <c r="L8" s="30" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M8" s="39" t="str" cm="1">
+      <c r="M8" s="32" t="str" cm="1">
         <f t="array" ref="M8">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -1955,11 +1959,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L9" s="37" t="str" cm="1">
+      <c r="L9" s="30" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M9" s="39" t="str" cm="1">
+      <c r="M9" s="32" t="str" cm="1">
         <f t="array" ref="M9">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -1999,11 +2003,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L10" s="37" t="str" cm="1">
+      <c r="L10" s="30" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M10" s="39" t="str" cm="1">
+      <c r="M10" s="32" t="str" cm="1">
         <f t="array" ref="M10">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -2043,32 +2047,32 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L11" s="37" t="str" cm="1">
+      <c r="L11" s="30" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M11" s="39" t="str" cm="1">
+      <c r="M11" s="32" t="str" cm="1">
         <f t="array" ref="M11">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N11" s="29" t="s">
+      <c r="N11" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
       <c r="T11" s="3">
         <f>COUNTIF(Table4[City],"SURAT")</f>
         <v>58</v>
       </c>
-      <c r="W11" s="35" t="s">
+      <c r="W11" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="42"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
@@ -2105,32 +2109,32 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L12" s="37" t="str" cm="1">
+      <c r="L12" s="30" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M12" s="39" t="str" cm="1">
+      <c r="M12" s="32" t="str" cm="1">
         <f t="array" ref="M12">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
-      <c r="N12" s="29" t="s">
+      <c r="N12" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
       <c r="T12" s="3">
         <f>SUMIF(Table4[Category],"Furniture",Table4[Sales])</f>
         <v>4902639.8900000025</v>
       </c>
-      <c r="W12" s="35" t="s">
+      <c r="W12" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="42"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
@@ -2167,32 +2171,32 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L13" s="37" t="str" cm="1">
+      <c r="L13" s="30" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M13" s="39" t="str" cm="1">
+      <c r="M13" s="32" t="str" cm="1">
         <f t="array" ref="M13">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N13" s="29" t="s">
+      <c r="N13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
       <c r="T13" s="3">
         <f>SUMIF(Table4[Region],"west",Table4[Quantity])</f>
         <v>83</v>
       </c>
-      <c r="W13" s="35" t="s">
+      <c r="W13" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="42"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
@@ -2229,22 +2233,22 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L14" s="37" t="str" cm="1">
+      <c r="L14" s="30" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M14" s="39" t="str" cm="1">
+      <c r="M14" s="32" t="str" cm="1">
         <f t="array" ref="M14">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N14" s="29" t="s">
+      <c r="N14" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
       <c r="T14" s="3">
         <f>AVERAGEIF(Table4[City],"Pune",Table4[Profit])</f>
         <v>5199.8313559322023</v>
@@ -2285,22 +2289,22 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L15" s="37" t="str" cm="1">
+      <c r="L15" s="30" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M15" s="39" t="str" cm="1">
+      <c r="M15" s="32" t="str" cm="1">
         <f t="array" ref="M15">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N15" s="29" t="s">
+      <c r="N15" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
       <c r="T15" s="3">
         <f>AVERAGEIF(Table4[Region],"North",Table4[Quantity])</f>
         <v>5.2534246575342465</v>
@@ -2344,22 +2348,22 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L16" s="37" t="str" cm="1">
+      <c r="L16" s="30" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M16" s="39" t="str" cm="1">
+      <c r="M16" s="32" t="str" cm="1">
         <f t="array" ref="M16">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
-      <c r="N16" s="29" t="s">
+      <c r="N16" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
       <c r="T16" s="3">
         <f>_xlfn.MAXIFS(Table4[Profit],Table4[State],"Gujarat")</f>
         <v>13586.56</v>
@@ -2367,13 +2371,13 @@
       <c r="W16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="X16" s="31" t="s">
+      <c r="X16" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="33"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="Y16" s="47"/>
+      <c r="Z16" s="48"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>16</v>
       </c>
@@ -2408,22 +2412,22 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L17" s="37" t="str" cm="1">
+      <c r="L17" s="30" t="str" cm="1">
         <f t="array" ref="L17">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M17" s="39" t="str" cm="1">
+      <c r="M17" s="32" t="str" cm="1">
         <f t="array" ref="M17">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N17" s="29" t="s">
+      <c r="N17" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
       <c r="T17" s="3">
         <f>AVERAGEIF(Table4[Product],"Laptop",Table4[Profit])</f>
         <v>4660.5817460317476</v>
@@ -2431,13 +2435,13 @@
       <c r="W17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="X17" s="30" t="s">
+      <c r="X17" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="Y17" s="45"/>
+      <c r="Z17" s="45"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -2472,28 +2476,28 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L18" s="37" t="str" cm="1">
+      <c r="L18" s="30" t="str" cm="1">
         <f t="array" ref="L18">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M18" s="39" t="str" cm="1">
+      <c r="M18" s="32" t="str" cm="1">
         <f t="array" ref="M18">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
       <c r="T18" s="5">
         <f>_xlfn.MINIFS(Table4[Sales],Table4[Region],"East")</f>
         <v>1072.04</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>18</v>
       </c>
@@ -2528,16 +2532,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L19" s="37" t="str" cm="1">
+      <c r="L19" s="30" t="str" cm="1">
         <f t="array" ref="L19">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M19" s="39" t="str" cm="1">
+      <c r="M19" s="32" t="str" cm="1">
         <f t="array" ref="M19">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -2572,16 +2576,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L20" s="37" t="str" cm="1">
+      <c r="L20" s="30" t="str" cm="1">
         <f t="array" ref="L20">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M20" s="39" t="str" cm="1">
+      <c r="M20" s="32" t="str" cm="1">
         <f t="array" ref="M20">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>20</v>
       </c>
@@ -2616,24 +2620,24 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L21" s="37" t="str" cm="1">
+      <c r="L21" s="30" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M21" s="39" t="str" cm="1">
+      <c r="M21" s="32" t="str" cm="1">
         <f t="array" ref="M21">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="P21" s="34" t="s">
+      <c r="P21" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -2668,17 +2672,17 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L22" s="37" t="str" cm="1">
+      <c r="L22" s="30" t="str" cm="1">
         <f t="array" ref="L22">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M22" s="39" t="str" cm="1">
+      <c r="M22" s="32" t="str" cm="1">
         <f t="array" ref="M22">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>22</v>
       </c>
@@ -2713,11 +2717,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L23" s="37" t="str" cm="1">
+      <c r="L23" s="30" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M23" s="39" t="str" cm="1">
+      <c r="M23" s="32" t="str" cm="1">
         <f t="array" ref="M23">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -2740,7 +2744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -2775,11 +2779,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L24" s="37" t="str" cm="1">
+      <c r="L24" s="30" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M24" s="39" t="str" cm="1">
+      <c r="M24" s="32" t="str" cm="1">
         <f t="array" ref="M24">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -2803,14 +2807,14 @@
         <f>COUNTIFS(Table4[Category],"Electronics",Table4[Product],"Tablet")</f>
         <v>55</v>
       </c>
-      <c r="X24" s="47" t="s">
+      <c r="X24" s="38" t="s">
         <v>89</v>
       </c>
       <c r="Y24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>24</v>
       </c>
@@ -2845,16 +2849,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L25" s="37" t="str" cm="1">
+      <c r="L25" s="30" t="str" cm="1">
         <f t="array" ref="L25">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M25" s="39" t="str" cm="1">
+      <c r="M25" s="32" t="str" cm="1">
         <f t="array" ref="M25">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -2889,16 +2893,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L26" s="37" t="str" cm="1">
+      <c r="L26" s="30" t="str" cm="1">
         <f t="array" ref="L26">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M26" s="39" t="str" cm="1">
+      <c r="M26" s="32" t="str" cm="1">
         <f t="array" ref="M26">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>26</v>
       </c>
@@ -2933,32 +2937,39 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L27" s="37" t="str" cm="1">
+      <c r="L27" s="30" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M27" s="39" t="str" cm="1">
+      <c r="M27" s="32" t="str" cm="1">
         <f t="array" ref="M27">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N27" s="29" t="s">
+      <c r="N27" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="44"/>
       <c r="X27" s="7">
         <f>SUMIFS(Table4[Sales],Table4[State],"Gujarat",Table4[Region],"South")</f>
         <v>1557137.2400000005</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF27" s="3">
+        <f>SUMIF(Table4[Region],"North",Table4[Profit])</f>
+        <v>627446.32000000018</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -2993,32 +3004,39 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L28" s="37" t="str" cm="1">
+      <c r="L28" s="30" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M28" s="39" t="str" cm="1">
+      <c r="M28" s="32" t="str" cm="1">
         <f t="array" ref="M28">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
-      <c r="N28" s="29" t="s">
+      <c r="N28" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="44"/>
       <c r="X28" s="7">
         <f>SUMIFS(Table4[Sales],Table4[State],"Gujarat",Table4[Region],"South",Table4[City],"ahmedabad")</f>
         <v>554700.17000000004</v>
       </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF28" s="3">
+        <f>SUMIF(Table4[Region],"South",Table4[Profit])</f>
+        <v>881288.17000000027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>28</v>
       </c>
@@ -3053,27 +3071,27 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L29" s="37" t="str" cm="1">
+      <c r="L29" s="30" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M29" s="39" t="str" cm="1">
+      <c r="M29" s="32" t="str" cm="1">
         <f t="array" ref="M29">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N29" s="29" t="s">
+      <c r="N29" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="38">
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="44"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="44"/>
+      <c r="X29" s="31">
         <f>SUMIFS(Table4[Quantity],Table4[Region],"North",Table4[State],"Gujarat",Table4[City],"Vadodara",Table4[Product],"Tablet")</f>
         <v>5</v>
       </c>
@@ -3089,8 +3107,15 @@
       <c r="AC29" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF29" s="3">
+        <f>SUMIF(Table4[Region],"East",Table4[Profit])</f>
+        <v>747590.95000000019</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -3125,30 +3150,34 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L30" s="37" t="str" cm="1">
+      <c r="L30" s="30" t="str" cm="1">
         <f t="array" ref="L30">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M30" s="39" t="str" cm="1">
+      <c r="M30" s="32" t="str" cm="1">
         <f t="array" ref="M30">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N30" s="29" t="s">
+      <c r="N30" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="29"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="44"/>
       <c r="X30" s="7">
         <f>MAX(Z30:AC30)</f>
         <v>881288.17000000027</v>
       </c>
+      <c r="Y30" t="str">
+        <f>VLOOKUP(MAX(AF27:AF30),CHOOSE({1,2},AF27:AF30,AE27:AE30),2,FALSE)</f>
+        <v>SOUTH</v>
+      </c>
       <c r="Z30" s="3">
         <f>SUMIF(Table4[Region],"North",Table4[Profit])</f>
         <v>627446.32000000018</v>
@@ -3165,8 +3194,15 @@
         <f>SUMIF(Table4[Region],"West",Table4[Profit])</f>
         <v>86233.62999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF30" s="3">
+        <f>SUMIF(Table4[Region],"West",Table4[Profit])</f>
+        <v>86233.62999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>30</v>
       </c>
@@ -3201,31 +3237,31 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L31" s="37" t="str" cm="1">
+      <c r="L31" s="30" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M31" s="39" t="str" cm="1">
+      <c r="M31" s="32" t="str" cm="1">
         <f t="array" ref="M31">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
-      <c r="N31" s="29" t="s">
+      <c r="N31" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="48" t="s">
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="39" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -3260,32 +3296,39 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L32" s="37" t="str" cm="1">
+      <c r="L32" s="30" t="str" cm="1">
         <f t="array" ref="L32">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M32" s="39" t="str" cm="1">
+      <c r="M32" s="32" t="str" cm="1">
         <f t="array" ref="M32">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N32" s="29" t="s">
+      <c r="N32" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="38">
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="31">
         <f>COUNTIFS(Table4[Product],"laptop",Table4[State],"Gujarat")</f>
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE32" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF32" s="3">
+        <f>SUMIF(Table4[Category],"CLOTHING",Table4[Quantity])</f>
+        <v>848</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>32</v>
       </c>
@@ -3320,27 +3363,27 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L33" s="37" t="str" cm="1">
+      <c r="L33" s="30" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M33" s="39" t="str" cm="1">
+      <c r="M33" s="32" t="str" cm="1">
         <f t="array" ref="M33">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
-      <c r="N33" s="29" t="s">
+      <c r="N33" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="38">
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="31">
         <f>SUMIFS(Table4[Profit],Table4[Product],"Jeans")</f>
         <v>241587.26000000004</v>
       </c>
@@ -3353,8 +3396,15 @@
       <c r="AB33" s="28" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE33" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF33" s="3">
+        <f>SUMIF(Table4[Category],"ELECTRONICS",Table4[Quantity])</f>
+        <v>924</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -3389,29 +3439,33 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L34" s="37" t="str" cm="1">
+      <c r="L34" s="30" t="str" cm="1">
         <f t="array" ref="L34">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M34" s="39" t="str" cm="1">
+      <c r="M34" s="32" t="str" cm="1">
         <f t="array" ref="M34">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N34" s="29" t="s">
+      <c r="N34" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="38">
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="31">
         <f>MAX(Z34:AB34)</f>
         <v>937</v>
+      </c>
+      <c r="Y34" t="str">
+        <f>INDEX(AE32:AE34,MATCH(MAX(AF32:AF34),AF32:AF34,0))</f>
+        <v>FURNITURE</v>
       </c>
       <c r="Z34" s="3">
         <f>SUMIF(Table4[Category],"CLOTHING",Table4[Quantity])</f>
@@ -3425,8 +3479,15 @@
         <f>SUMIF(Table4[Category],"FURNITURE",Table4[Quantity])</f>
         <v>937</v>
       </c>
-    </row>
-    <row r="35" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE34" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF34" s="3">
+        <f>SUMIF(Table4[Category],"FURNITURE",Table4[Quantity])</f>
+        <v>937</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18">
         <v>34</v>
       </c>
@@ -3461,32 +3522,32 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L35" s="37" t="str" cm="1">
+      <c r="L35" s="30" t="str" cm="1">
         <f t="array" ref="L35">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M35" s="39" t="str" cm="1">
+      <c r="M35" s="32" t="str" cm="1">
         <f t="array" ref="M35">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
-      <c r="N35" s="29" t="s">
+      <c r="N35" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="44"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="44"/>
       <c r="X35" s="7">
         <f>SUMIFS(Table4[Sales],Table4[Product],"Mobile",Table4[Region],"South",Table4[State],"Maharashtra",Table4[City],"Pune")</f>
         <v>30927.86</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -3521,26 +3582,26 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L36" s="37" t="str" cm="1">
+      <c r="L36" s="30" t="str" cm="1">
         <f t="array" ref="L36">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M36" s="39" t="str" cm="1">
+      <c r="M36" s="32" t="str" cm="1">
         <f t="array" ref="M36">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
-      <c r="N36" s="29" t="s">
+      <c r="N36" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="44"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="44"/>
+      <c r="V36" s="44"/>
+      <c r="W36" s="44"/>
       <c r="X36" s="7">
         <f>SUMIFS(Table4[Quantity],Table4[Product],"Sofa",Table4[Region],"North",Table4[State],"Gujarat",Table4[City],"Ahmedabad")</f>
         <v>6</v>
@@ -3554,7 +3615,7 @@
       </c>
       <c r="AC36" s="41"/>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" s="18">
         <v>36</v>
       </c>
@@ -3589,48 +3650,52 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L37" s="37" t="str" cm="1">
+      <c r="L37" s="30" t="str" cm="1">
         <f t="array" ref="L37">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M37" s="39" t="str" cm="1">
+      <c r="M37" s="32" t="str" cm="1">
         <f t="array" ref="M37">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N37" s="29" t="s">
+      <c r="N37" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="38">
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="44"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="31">
         <f>MAX(AA37:AA39)</f>
         <v>293616.65000000008</v>
       </c>
-      <c r="Z37" s="42" t="str" cm="1">
+      <c r="Y37" t="str">
+        <f>INDEX(Z37:Z39,MATCH(MAX(AA37:AA39),AA37:AA39,0))</f>
+        <v>Laptop</v>
+      </c>
+      <c r="Z37" s="33" t="str" cm="1">
         <f t="array" ref="Z37:Z39">_xlfn.UNIQUE(_xlfn._xlws.FILTER(G2:G501,F2:F501="Electronics"))</f>
         <v>Mobile</v>
       </c>
-      <c r="AA37" s="43">
+      <c r="AA37" s="34">
         <f>SUMIF(Table4[Product],"Mobile",Table4[Profit])</f>
         <v>271457.8899999999</v>
       </c>
-      <c r="AB37" s="42" t="str" cm="1">
+      <c r="AB37" s="33" t="str" cm="1">
         <f t="array" ref="AB37:AB39">_xlfn.UNIQUE(_xlfn._xlws.FILTER(G2:G501,F2:F501="Clothing"))</f>
         <v>Jeans</v>
       </c>
-      <c r="AC37" s="43">
+      <c r="AC37" s="34">
         <f>SUMIF(Table4[Product],"Jeans",Table4[Profit])</f>
         <v>241587.26000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -3665,46 +3730,50 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L38" s="37" t="str" cm="1">
+      <c r="L38" s="30" t="str" cm="1">
         <f t="array" ref="L38">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M38" s="39" t="str" cm="1">
+      <c r="M38" s="32" t="str" cm="1">
         <f t="array" ref="M38">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="N38" s="29" t="s">
+      <c r="N38" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="38">
+      <c r="O38" s="44"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="31">
         <f>MAX(AC37:AC39)</f>
         <v>271882.18999999994</v>
       </c>
-      <c r="Z38" s="42" t="str">
+      <c r="Y38" t="str">
+        <f>INDEX(_xlfn.ANCHORARRAY(AB37),MATCH(MAX(AC37:AC39),AC37:AC39,0))</f>
+        <v>Jacket</v>
+      </c>
+      <c r="Z38" s="33" t="str">
         <v>Tablet</v>
       </c>
-      <c r="AA38" s="43">
+      <c r="AA38" s="34">
         <f>SUMIF(Table4[Product],"Tablet",Table4[Profit])</f>
         <v>247695.39000000004</v>
       </c>
-      <c r="AB38" s="42" t="str">
+      <c r="AB38" s="33" t="str">
         <v>Shirt</v>
       </c>
-      <c r="AC38" s="43">
+      <c r="AC38" s="34">
         <f>SUMIF(Table4[Product],"Shirt",Table4[Profit])</f>
         <v>268297.41000000009</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18">
         <v>38</v>
       </c>
@@ -3739,30 +3808,30 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L39" s="37" t="str" cm="1">
+      <c r="L39" s="30" t="str" cm="1">
         <f t="array" ref="L39">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M39" s="39" t="str" cm="1">
+      <c r="M39" s="32" t="str" cm="1">
         <f t="array" ref="M39">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
-      <c r="Z39" s="44" t="str">
+      <c r="Z39" s="35" t="str">
         <v>Laptop</v>
       </c>
-      <c r="AA39" s="45">
+      <c r="AA39" s="36">
         <f>SUMIF(Table4[Product],"Laptop",Table4[Profit])</f>
         <v>293616.65000000008</v>
       </c>
-      <c r="AB39" s="44" t="str">
+      <c r="AB39" s="35" t="str">
         <v>Jacket</v>
       </c>
-      <c r="AC39" s="43">
+      <c r="AC39" s="34">
         <f>SUMIF(Table4[Product],"Jacket",Table4[Profit])</f>
         <v>271882.18999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -3797,16 +3866,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L40" s="37" t="str" cm="1">
+      <c r="L40" s="30" t="str" cm="1">
         <f t="array" ref="L40">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M40" s="39" t="str" cm="1">
+      <c r="M40" s="32" t="str" cm="1">
         <f t="array" ref="M40">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" s="18">
         <v>40</v>
       </c>
@@ -3841,16 +3910,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L41" s="37" t="str" cm="1">
+      <c r="L41" s="30" t="str" cm="1">
         <f t="array" ref="L41">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M41" s="39" t="str" cm="1">
+      <c r="M41" s="32" t="str" cm="1">
         <f t="array" ref="M41">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -3885,16 +3954,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L42" s="37" t="str" cm="1">
+      <c r="L42" s="30" t="str" cm="1">
         <f t="array" ref="L42">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M42" s="39" t="str" cm="1">
+      <c r="M42" s="32" t="str" cm="1">
         <f t="array" ref="M42">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" s="18">
         <v>42</v>
       </c>
@@ -3929,16 +3998,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L43" s="37" t="str" cm="1">
+      <c r="L43" s="30" t="str" cm="1">
         <f t="array" ref="L43">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M43" s="39" t="str" cm="1">
+      <c r="M43" s="32" t="str" cm="1">
         <f t="array" ref="M43">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -3973,16 +4042,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L44" s="37" t="str" cm="1">
+      <c r="L44" s="30" t="str" cm="1">
         <f t="array" ref="L44">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M44" s="39" t="str" cm="1">
+      <c r="M44" s="32" t="str" cm="1">
         <f t="array" ref="M44">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -4017,16 +4086,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L45" s="37" t="str" cm="1">
+      <c r="L45" s="30" t="str" cm="1">
         <f t="array" ref="L45">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M45" s="39" t="str" cm="1">
+      <c r="M45" s="32" t="str" cm="1">
         <f t="array" ref="M45">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -4061,16 +4130,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L46" s="37" t="str" cm="1">
+      <c r="L46" s="30" t="str" cm="1">
         <f t="array" ref="L46">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M46" s="39" t="str" cm="1">
+      <c r="M46" s="32" t="str" cm="1">
         <f t="array" ref="M46">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -4105,16 +4174,16 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L47" s="37" t="str" cm="1">
+      <c r="L47" s="30" t="str" cm="1">
         <f t="array" ref="L47">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M47" s="39" t="str" cm="1">
+      <c r="M47" s="32" t="str" cm="1">
         <f t="array" ref="M47">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -4149,11 +4218,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L48" s="37" t="str" cm="1">
+      <c r="L48" s="30" t="str" cm="1">
         <f t="array" ref="L48">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M48" s="39" t="str" cm="1">
+      <c r="M48" s="32" t="str" cm="1">
         <f t="array" ref="M48">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4193,11 +4262,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L49" s="37" t="str" cm="1">
+      <c r="L49" s="30" t="str" cm="1">
         <f t="array" ref="L49">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M49" s="39" t="str" cm="1">
+      <c r="M49" s="32" t="str" cm="1">
         <f t="array" ref="M49">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -4237,11 +4306,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L50" s="37" t="str" cm="1">
+      <c r="L50" s="30" t="str" cm="1">
         <f t="array" ref="L50">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M50" s="39" t="str" cm="1">
+      <c r="M50" s="32" t="str" cm="1">
         <f t="array" ref="M50">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4281,11 +4350,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L51" s="37" t="str" cm="1">
+      <c r="L51" s="30" t="str" cm="1">
         <f t="array" ref="L51">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M51" s="39" t="str" cm="1">
+      <c r="M51" s="32" t="str" cm="1">
         <f t="array" ref="M51">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4325,11 +4394,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L52" s="37" t="str" cm="1">
+      <c r="L52" s="30" t="str" cm="1">
         <f t="array" ref="L52">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M52" s="39" t="str" cm="1">
+      <c r="M52" s="32" t="str" cm="1">
         <f t="array" ref="M52">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4369,11 +4438,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L53" s="37" t="str" cm="1">
+      <c r="L53" s="30" t="str" cm="1">
         <f t="array" ref="L53">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M53" s="39" t="str" cm="1">
+      <c r="M53" s="32" t="str" cm="1">
         <f t="array" ref="M53">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4413,11 +4482,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L54" s="37" t="str" cm="1">
+      <c r="L54" s="30" t="str" cm="1">
         <f t="array" ref="L54">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M54" s="39" t="str" cm="1">
+      <c r="M54" s="32" t="str" cm="1">
         <f t="array" ref="M54">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -4457,11 +4526,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L55" s="37" t="str" cm="1">
+      <c r="L55" s="30" t="str" cm="1">
         <f t="array" ref="L55">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M55" s="39" t="str" cm="1">
+      <c r="M55" s="32" t="str" cm="1">
         <f t="array" ref="M55">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4501,11 +4570,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L56" s="37" t="str" cm="1">
+      <c r="L56" s="30" t="str" cm="1">
         <f t="array" ref="L56">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M56" s="39" t="str" cm="1">
+      <c r="M56" s="32" t="str" cm="1">
         <f t="array" ref="M56">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4545,11 +4614,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L57" s="37" t="str" cm="1">
+      <c r="L57" s="30" t="str" cm="1">
         <f t="array" ref="L57">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M57" s="39" t="str" cm="1">
+      <c r="M57" s="32" t="str" cm="1">
         <f t="array" ref="M57">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4589,11 +4658,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L58" s="37" t="str" cm="1">
+      <c r="L58" s="30" t="str" cm="1">
         <f t="array" ref="L58">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M58" s="39" t="str" cm="1">
+      <c r="M58" s="32" t="str" cm="1">
         <f t="array" ref="M58">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -4633,11 +4702,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L59" s="37" t="str" cm="1">
+      <c r="L59" s="30" t="str" cm="1">
         <f t="array" ref="L59">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M59" s="39" t="str" cm="1">
+      <c r="M59" s="32" t="str" cm="1">
         <f t="array" ref="M59">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4677,11 +4746,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L60" s="37" t="str" cm="1">
+      <c r="L60" s="30" t="str" cm="1">
         <f t="array" ref="L60">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M60" s="39" t="str" cm="1">
+      <c r="M60" s="32" t="str" cm="1">
         <f t="array" ref="M60">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -4721,11 +4790,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L61" s="37" t="str" cm="1">
+      <c r="L61" s="30" t="str" cm="1">
         <f t="array" ref="L61">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M61" s="39" t="str" cm="1">
+      <c r="M61" s="32" t="str" cm="1">
         <f t="array" ref="M61">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4765,11 +4834,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L62" s="37" t="str" cm="1">
+      <c r="L62" s="30" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M62" s="39" t="str" cm="1">
+      <c r="M62" s="32" t="str" cm="1">
         <f t="array" ref="M62">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4809,11 +4878,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L63" s="37" t="str" cm="1">
+      <c r="L63" s="30" t="str" cm="1">
         <f t="array" ref="L63">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M63" s="39" t="str" cm="1">
+      <c r="M63" s="32" t="str" cm="1">
         <f t="array" ref="M63">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -4853,11 +4922,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L64" s="37" t="str" cm="1">
+      <c r="L64" s="30" t="str" cm="1">
         <f t="array" ref="L64">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M64" s="39" t="str" cm="1">
+      <c r="M64" s="32" t="str" cm="1">
         <f t="array" ref="M64">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4897,11 +4966,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L65" s="37" t="str" cm="1">
+      <c r="L65" s="30" t="str" cm="1">
         <f t="array" ref="L65">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M65" s="39" t="str" cm="1">
+      <c r="M65" s="32" t="str" cm="1">
         <f t="array" ref="M65">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -4941,11 +5010,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L66" s="37" t="str" cm="1">
+      <c r="L66" s="30" t="str" cm="1">
         <f t="array" ref="L66">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M66" s="39" t="str" cm="1">
+      <c r="M66" s="32" t="str" cm="1">
         <f t="array" ref="M66">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -4985,11 +5054,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L67" s="37" t="str" cm="1">
+      <c r="L67" s="30" t="str" cm="1">
         <f t="array" ref="L67">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M67" s="39" t="str" cm="1">
+      <c r="M67" s="32" t="str" cm="1">
         <f t="array" ref="M67">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5029,11 +5098,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L68" s="37" t="str" cm="1">
+      <c r="L68" s="30" t="str" cm="1">
         <f t="array" ref="L68">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M68" s="39" t="str" cm="1">
+      <c r="M68" s="32" t="str" cm="1">
         <f t="array" ref="M68">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -5073,11 +5142,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L69" s="37" t="str" cm="1">
+      <c r="L69" s="30" t="str" cm="1">
         <f t="array" ref="L69">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M69" s="39" t="str" cm="1">
+      <c r="M69" s="32" t="str" cm="1">
         <f t="array" ref="M69">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5117,11 +5186,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L70" s="37" t="str" cm="1">
+      <c r="L70" s="30" t="str" cm="1">
         <f t="array" ref="L70">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M70" s="39" t="str" cm="1">
+      <c r="M70" s="32" t="str" cm="1">
         <f t="array" ref="M70">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5161,11 +5230,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L71" s="37" t="str" cm="1">
+      <c r="L71" s="30" t="str" cm="1">
         <f t="array" ref="L71">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M71" s="39" t="str" cm="1">
+      <c r="M71" s="32" t="str" cm="1">
         <f t="array" ref="M71">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5205,11 +5274,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L72" s="37" t="str" cm="1">
+      <c r="L72" s="30" t="str" cm="1">
         <f t="array" ref="L72">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M72" s="39" t="str" cm="1">
+      <c r="M72" s="32" t="str" cm="1">
         <f t="array" ref="M72">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5249,11 +5318,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L73" s="37" t="str" cm="1">
+      <c r="L73" s="30" t="str" cm="1">
         <f t="array" ref="L73">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M73" s="39" t="str" cm="1">
+      <c r="M73" s="32" t="str" cm="1">
         <f t="array" ref="M73">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -5293,11 +5362,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L74" s="37" t="str" cm="1">
+      <c r="L74" s="30" t="str" cm="1">
         <f t="array" ref="L74">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M74" s="39" t="str" cm="1">
+      <c r="M74" s="32" t="str" cm="1">
         <f t="array" ref="M74">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5337,11 +5406,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L75" s="37" t="str" cm="1">
+      <c r="L75" s="30" t="str" cm="1">
         <f t="array" ref="L75">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M75" s="39" t="str" cm="1">
+      <c r="M75" s="32" t="str" cm="1">
         <f t="array" ref="M75">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -5381,11 +5450,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L76" s="37" t="str" cm="1">
+      <c r="L76" s="30" t="str" cm="1">
         <f t="array" ref="L76">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M76" s="39" t="str" cm="1">
+      <c r="M76" s="32" t="str" cm="1">
         <f t="array" ref="M76">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -5425,11 +5494,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L77" s="37" t="str" cm="1">
+      <c r="L77" s="30" t="str" cm="1">
         <f t="array" ref="L77">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M77" s="39" t="str" cm="1">
+      <c r="M77" s="32" t="str" cm="1">
         <f t="array" ref="M77">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5469,11 +5538,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L78" s="37" t="str" cm="1">
+      <c r="L78" s="30" t="str" cm="1">
         <f t="array" ref="L78">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M78" s="39" t="str" cm="1">
+      <c r="M78" s="32" t="str" cm="1">
         <f t="array" ref="M78">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5513,11 +5582,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L79" s="37" t="str" cm="1">
+      <c r="L79" s="30" t="str" cm="1">
         <f t="array" ref="L79">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M79" s="39" t="str" cm="1">
+      <c r="M79" s="32" t="str" cm="1">
         <f t="array" ref="M79">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -5557,11 +5626,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L80" s="37" t="str" cm="1">
+      <c r="L80" s="30" t="str" cm="1">
         <f t="array" ref="L80">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M80" s="39" t="str" cm="1">
+      <c r="M80" s="32" t="str" cm="1">
         <f t="array" ref="M80">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5601,11 +5670,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L81" s="37" t="str" cm="1">
+      <c r="L81" s="30" t="str" cm="1">
         <f t="array" ref="L81">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M81" s="39" t="str" cm="1">
+      <c r="M81" s="32" t="str" cm="1">
         <f t="array" ref="M81">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5645,11 +5714,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L82" s="37" t="str" cm="1">
+      <c r="L82" s="30" t="str" cm="1">
         <f t="array" ref="L82">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M82" s="39" t="str" cm="1">
+      <c r="M82" s="32" t="str" cm="1">
         <f t="array" ref="M82">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5689,11 +5758,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L83" s="37" t="str" cm="1">
+      <c r="L83" s="30" t="str" cm="1">
         <f t="array" ref="L83">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M83" s="39" t="str" cm="1">
+      <c r="M83" s="32" t="str" cm="1">
         <f t="array" ref="M83">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5733,11 +5802,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L84" s="37" t="str" cm="1">
+      <c r="L84" s="30" t="str" cm="1">
         <f t="array" ref="L84">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M84" s="39" t="str" cm="1">
+      <c r="M84" s="32" t="str" cm="1">
         <f t="array" ref="M84">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5777,11 +5846,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L85" s="37" t="str" cm="1">
+      <c r="L85" s="30" t="str" cm="1">
         <f t="array" ref="L85">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M85" s="39" t="str" cm="1">
+      <c r="M85" s="32" t="str" cm="1">
         <f t="array" ref="M85">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5821,11 +5890,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L86" s="37" t="str" cm="1">
+      <c r="L86" s="30" t="str" cm="1">
         <f t="array" ref="L86">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M86" s="39" t="str" cm="1">
+      <c r="M86" s="32" t="str" cm="1">
         <f t="array" ref="M86">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5865,11 +5934,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L87" s="37" t="str" cm="1">
+      <c r="L87" s="30" t="str" cm="1">
         <f t="array" ref="L87">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M87" s="39" t="str" cm="1">
+      <c r="M87" s="32" t="str" cm="1">
         <f t="array" ref="M87">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -5909,11 +5978,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L88" s="37" t="str" cm="1">
+      <c r="L88" s="30" t="str" cm="1">
         <f t="array" ref="L88">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M88" s="39" t="str" cm="1">
+      <c r="M88" s="32" t="str" cm="1">
         <f t="array" ref="M88">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -5953,11 +6022,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L89" s="37" t="str" cm="1">
+      <c r="L89" s="30" t="str" cm="1">
         <f t="array" ref="L89">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M89" s="39" t="str" cm="1">
+      <c r="M89" s="32" t="str" cm="1">
         <f t="array" ref="M89">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -5997,11 +6066,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L90" s="37" t="str" cm="1">
+      <c r="L90" s="30" t="str" cm="1">
         <f t="array" ref="L90">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M90" s="39" t="str" cm="1">
+      <c r="M90" s="32" t="str" cm="1">
         <f t="array" ref="M90">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6041,11 +6110,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L91" s="37" t="str" cm="1">
+      <c r="L91" s="30" t="str" cm="1">
         <f t="array" ref="L91">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M91" s="39" t="str" cm="1">
+      <c r="M91" s="32" t="str" cm="1">
         <f t="array" ref="M91">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6085,11 +6154,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L92" s="37" t="str" cm="1">
+      <c r="L92" s="30" t="str" cm="1">
         <f t="array" ref="L92">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M92" s="39" t="str" cm="1">
+      <c r="M92" s="32" t="str" cm="1">
         <f t="array" ref="M92">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6129,11 +6198,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L93" s="37" t="str" cm="1">
+      <c r="L93" s="30" t="str" cm="1">
         <f t="array" ref="L93">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M93" s="39" t="str" cm="1">
+      <c r="M93" s="32" t="str" cm="1">
         <f t="array" ref="M93">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6173,11 +6242,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L94" s="37" t="str" cm="1">
+      <c r="L94" s="30" t="str" cm="1">
         <f t="array" ref="L94">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M94" s="39" t="str" cm="1">
+      <c r="M94" s="32" t="str" cm="1">
         <f t="array" ref="M94">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6217,11 +6286,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L95" s="37" t="str" cm="1">
+      <c r="L95" s="30" t="str" cm="1">
         <f t="array" ref="L95">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M95" s="39" t="str" cm="1">
+      <c r="M95" s="32" t="str" cm="1">
         <f t="array" ref="M95">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6261,11 +6330,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L96" s="37" t="str" cm="1">
+      <c r="L96" s="30" t="str" cm="1">
         <f t="array" ref="L96">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M96" s="39" t="str" cm="1">
+      <c r="M96" s="32" t="str" cm="1">
         <f t="array" ref="M96">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6305,11 +6374,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L97" s="37" t="str" cm="1">
+      <c r="L97" s="30" t="str" cm="1">
         <f t="array" ref="L97">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M97" s="39" t="str" cm="1">
+      <c r="M97" s="32" t="str" cm="1">
         <f t="array" ref="M97">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6349,11 +6418,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L98" s="37" t="str" cm="1">
+      <c r="L98" s="30" t="str" cm="1">
         <f t="array" ref="L98">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M98" s="39" t="str" cm="1">
+      <c r="M98" s="32" t="str" cm="1">
         <f t="array" ref="M98">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6393,11 +6462,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L99" s="37" t="str" cm="1">
+      <c r="L99" s="30" t="str" cm="1">
         <f t="array" ref="L99">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M99" s="39" t="str" cm="1">
+      <c r="M99" s="32" t="str" cm="1">
         <f t="array" ref="M99">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6437,11 +6506,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L100" s="37" t="str" cm="1">
+      <c r="L100" s="30" t="str" cm="1">
         <f t="array" ref="L100">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M100" s="39" t="str" cm="1">
+      <c r="M100" s="32" t="str" cm="1">
         <f t="array" ref="M100">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6481,11 +6550,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L101" s="37" t="str" cm="1">
+      <c r="L101" s="30" t="str" cm="1">
         <f t="array" ref="L101">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M101" s="39" t="str" cm="1">
+      <c r="M101" s="32" t="str" cm="1">
         <f t="array" ref="M101">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6525,11 +6594,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L102" s="37" t="str" cm="1">
+      <c r="L102" s="30" t="str" cm="1">
         <f t="array" ref="L102">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M102" s="39" t="str" cm="1">
+      <c r="M102" s="32" t="str" cm="1">
         <f t="array" ref="M102">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6569,11 +6638,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L103" s="37" t="str" cm="1">
+      <c r="L103" s="30" t="str" cm="1">
         <f t="array" ref="L103">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M103" s="39" t="str" cm="1">
+      <c r="M103" s="32" t="str" cm="1">
         <f t="array" ref="M103">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6613,11 +6682,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L104" s="37" t="str" cm="1">
+      <c r="L104" s="30" t="str" cm="1">
         <f t="array" ref="L104">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M104" s="39" t="str" cm="1">
+      <c r="M104" s="32" t="str" cm="1">
         <f t="array" ref="M104">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6657,11 +6726,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L105" s="37" t="str" cm="1">
+      <c r="L105" s="30" t="str" cm="1">
         <f t="array" ref="L105">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M105" s="39" t="str" cm="1">
+      <c r="M105" s="32" t="str" cm="1">
         <f t="array" ref="M105">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6701,11 +6770,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L106" s="37" t="str" cm="1">
+      <c r="L106" s="30" t="str" cm="1">
         <f t="array" ref="L106">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M106" s="39" t="str" cm="1">
+      <c r="M106" s="32" t="str" cm="1">
         <f t="array" ref="M106">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6745,11 +6814,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L107" s="37" t="str" cm="1">
+      <c r="L107" s="30" t="str" cm="1">
         <f t="array" ref="L107">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M107" s="39" t="str" cm="1">
+      <c r="M107" s="32" t="str" cm="1">
         <f t="array" ref="M107">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -6789,11 +6858,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L108" s="37" t="str" cm="1">
+      <c r="L108" s="30" t="str" cm="1">
         <f t="array" ref="L108">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M108" s="39" t="str" cm="1">
+      <c r="M108" s="32" t="str" cm="1">
         <f t="array" ref="M108">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6833,11 +6902,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L109" s="37" t="str" cm="1">
+      <c r="L109" s="30" t="str" cm="1">
         <f t="array" ref="L109">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M109" s="39" t="str" cm="1">
+      <c r="M109" s="32" t="str" cm="1">
         <f t="array" ref="M109">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6877,11 +6946,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L110" s="37" t="str" cm="1">
+      <c r="L110" s="30" t="str" cm="1">
         <f t="array" ref="L110">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M110" s="39" t="str" cm="1">
+      <c r="M110" s="32" t="str" cm="1">
         <f t="array" ref="M110">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6921,11 +6990,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L111" s="37" t="str" cm="1">
+      <c r="L111" s="30" t="str" cm="1">
         <f t="array" ref="L111">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M111" s="39" t="str" cm="1">
+      <c r="M111" s="32" t="str" cm="1">
         <f t="array" ref="M111">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -6965,11 +7034,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L112" s="37" t="str" cm="1">
+      <c r="L112" s="30" t="str" cm="1">
         <f t="array" ref="L112">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M112" s="39" t="str" cm="1">
+      <c r="M112" s="32" t="str" cm="1">
         <f t="array" ref="M112">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7009,11 +7078,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L113" s="37" t="str" cm="1">
+      <c r="L113" s="30" t="str" cm="1">
         <f t="array" ref="L113">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M113" s="39" t="str" cm="1">
+      <c r="M113" s="32" t="str" cm="1">
         <f t="array" ref="M113">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7053,11 +7122,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L114" s="37" t="str" cm="1">
+      <c r="L114" s="30" t="str" cm="1">
         <f t="array" ref="L114">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M114" s="39" t="str" cm="1">
+      <c r="M114" s="32" t="str" cm="1">
         <f t="array" ref="M114">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7097,11 +7166,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L115" s="37" t="str" cm="1">
+      <c r="L115" s="30" t="str" cm="1">
         <f t="array" ref="L115">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M115" s="39" t="str" cm="1">
+      <c r="M115" s="32" t="str" cm="1">
         <f t="array" ref="M115">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7141,11 +7210,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L116" s="37" t="str" cm="1">
+      <c r="L116" s="30" t="str" cm="1">
         <f t="array" ref="L116">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M116" s="39" t="str" cm="1">
+      <c r="M116" s="32" t="str" cm="1">
         <f t="array" ref="M116">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7185,11 +7254,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L117" s="37" t="str" cm="1">
+      <c r="L117" s="30" t="str" cm="1">
         <f t="array" ref="L117">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M117" s="39" t="str" cm="1">
+      <c r="M117" s="32" t="str" cm="1">
         <f t="array" ref="M117">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7229,11 +7298,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L118" s="37" t="str" cm="1">
+      <c r="L118" s="30" t="str" cm="1">
         <f t="array" ref="L118">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M118" s="39" t="str" cm="1">
+      <c r="M118" s="32" t="str" cm="1">
         <f t="array" ref="M118">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -7273,11 +7342,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L119" s="37" t="str" cm="1">
+      <c r="L119" s="30" t="str" cm="1">
         <f t="array" ref="L119">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M119" s="39" t="str" cm="1">
+      <c r="M119" s="32" t="str" cm="1">
         <f t="array" ref="M119">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7317,11 +7386,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L120" s="37" t="str" cm="1">
+      <c r="L120" s="30" t="str" cm="1">
         <f t="array" ref="L120">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M120" s="39" t="str" cm="1">
+      <c r="M120" s="32" t="str" cm="1">
         <f t="array" ref="M120">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7361,11 +7430,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L121" s="37" t="str" cm="1">
+      <c r="L121" s="30" t="str" cm="1">
         <f t="array" ref="L121">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M121" s="39" t="str" cm="1">
+      <c r="M121" s="32" t="str" cm="1">
         <f t="array" ref="M121">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7405,11 +7474,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L122" s="37" t="str" cm="1">
+      <c r="L122" s="30" t="str" cm="1">
         <f t="array" ref="L122">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M122" s="39" t="str" cm="1">
+      <c r="M122" s="32" t="str" cm="1">
         <f t="array" ref="M122">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7449,11 +7518,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L123" s="37" t="str" cm="1">
+      <c r="L123" s="30" t="str" cm="1">
         <f t="array" ref="L123">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M123" s="39" t="str" cm="1">
+      <c r="M123" s="32" t="str" cm="1">
         <f t="array" ref="M123">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7493,11 +7562,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L124" s="37" t="str" cm="1">
+      <c r="L124" s="30" t="str" cm="1">
         <f t="array" ref="L124">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M124" s="39" t="str" cm="1">
+      <c r="M124" s="32" t="str" cm="1">
         <f t="array" ref="M124">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -7537,11 +7606,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L125" s="37" t="str" cm="1">
+      <c r="L125" s="30" t="str" cm="1">
         <f t="array" ref="L125">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M125" s="39" t="str" cm="1">
+      <c r="M125" s="32" t="str" cm="1">
         <f t="array" ref="M125">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7581,11 +7650,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L126" s="37" t="str" cm="1">
+      <c r="L126" s="30" t="str" cm="1">
         <f t="array" ref="L126">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M126" s="39" t="str" cm="1">
+      <c r="M126" s="32" t="str" cm="1">
         <f t="array" ref="M126">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7625,11 +7694,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L127" s="37" t="str" cm="1">
+      <c r="L127" s="30" t="str" cm="1">
         <f t="array" ref="L127">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M127" s="39" t="str" cm="1">
+      <c r="M127" s="32" t="str" cm="1">
         <f t="array" ref="M127">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7669,11 +7738,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L128" s="37" t="str" cm="1">
+      <c r="L128" s="30" t="str" cm="1">
         <f t="array" ref="L128">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M128" s="39" t="str" cm="1">
+      <c r="M128" s="32" t="str" cm="1">
         <f t="array" ref="M128">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7713,11 +7782,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L129" s="37" t="str" cm="1">
+      <c r="L129" s="30" t="str" cm="1">
         <f t="array" ref="L129">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M129" s="39" t="str" cm="1">
+      <c r="M129" s="32" t="str" cm="1">
         <f t="array" ref="M129">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7757,11 +7826,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L130" s="37" t="str" cm="1">
+      <c r="L130" s="30" t="str" cm="1">
         <f t="array" ref="L130">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M130" s="39" t="str" cm="1">
+      <c r="M130" s="32" t="str" cm="1">
         <f t="array" ref="M130">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7801,11 +7870,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L131" s="37" t="str" cm="1">
+      <c r="L131" s="30" t="str" cm="1">
         <f t="array" ref="L131">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M131" s="39" t="str" cm="1">
+      <c r="M131" s="32" t="str" cm="1">
         <f t="array" ref="M131">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7845,11 +7914,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L132" s="37" t="str" cm="1">
+      <c r="L132" s="30" t="str" cm="1">
         <f t="array" ref="L132">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M132" s="39" t="str" cm="1">
+      <c r="M132" s="32" t="str" cm="1">
         <f t="array" ref="M132">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7889,11 +7958,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L133" s="37" t="str" cm="1">
+      <c r="L133" s="30" t="str" cm="1">
         <f t="array" ref="L133">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M133" s="39" t="str" cm="1">
+      <c r="M133" s="32" t="str" cm="1">
         <f t="array" ref="M133">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -7933,11 +8002,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L134" s="37" t="str" cm="1">
+      <c r="L134" s="30" t="str" cm="1">
         <f t="array" ref="L134">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M134" s="39" t="str" cm="1">
+      <c r="M134" s="32" t="str" cm="1">
         <f t="array" ref="M134">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -7977,11 +8046,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L135" s="37" t="str" cm="1">
+      <c r="L135" s="30" t="str" cm="1">
         <f t="array" ref="L135">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M135" s="39" t="str" cm="1">
+      <c r="M135" s="32" t="str" cm="1">
         <f t="array" ref="M135">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8021,11 +8090,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L136" s="37" t="str" cm="1">
+      <c r="L136" s="30" t="str" cm="1">
         <f t="array" ref="L136">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M136" s="39" t="str" cm="1">
+      <c r="M136" s="32" t="str" cm="1">
         <f t="array" ref="M136">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -8065,11 +8134,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L137" s="37" t="str" cm="1">
+      <c r="L137" s="30" t="str" cm="1">
         <f t="array" ref="L137">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M137" s="39" t="str" cm="1">
+      <c r="M137" s="32" t="str" cm="1">
         <f t="array" ref="M137">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8109,11 +8178,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L138" s="37" t="str" cm="1">
+      <c r="L138" s="30" t="str" cm="1">
         <f t="array" ref="L138">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M138" s="39" t="str" cm="1">
+      <c r="M138" s="32" t="str" cm="1">
         <f t="array" ref="M138">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8153,11 +8222,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L139" s="37" t="str" cm="1">
+      <c r="L139" s="30" t="str" cm="1">
         <f t="array" ref="L139">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M139" s="39" t="str" cm="1">
+      <c r="M139" s="32" t="str" cm="1">
         <f t="array" ref="M139">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8197,11 +8266,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L140" s="37" t="str" cm="1">
+      <c r="L140" s="30" t="str" cm="1">
         <f t="array" ref="L140">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M140" s="39" t="str" cm="1">
+      <c r="M140" s="32" t="str" cm="1">
         <f t="array" ref="M140">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8241,11 +8310,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L141" s="37" t="str" cm="1">
+      <c r="L141" s="30" t="str" cm="1">
         <f t="array" ref="L141">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M141" s="39" t="str" cm="1">
+      <c r="M141" s="32" t="str" cm="1">
         <f t="array" ref="M141">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8285,11 +8354,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L142" s="37" t="str" cm="1">
+      <c r="L142" s="30" t="str" cm="1">
         <f t="array" ref="L142">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M142" s="39" t="str" cm="1">
+      <c r="M142" s="32" t="str" cm="1">
         <f t="array" ref="M142">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -8329,11 +8398,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L143" s="37" t="str" cm="1">
+      <c r="L143" s="30" t="str" cm="1">
         <f t="array" ref="L143">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M143" s="39" t="str" cm="1">
+      <c r="M143" s="32" t="str" cm="1">
         <f t="array" ref="M143">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8373,11 +8442,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L144" s="37" t="str" cm="1">
+      <c r="L144" s="30" t="str" cm="1">
         <f t="array" ref="L144">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M144" s="39" t="str" cm="1">
+      <c r="M144" s="32" t="str" cm="1">
         <f t="array" ref="M144">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8417,11 +8486,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L145" s="37" t="str" cm="1">
+      <c r="L145" s="30" t="str" cm="1">
         <f t="array" ref="L145">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M145" s="39" t="str" cm="1">
+      <c r="M145" s="32" t="str" cm="1">
         <f t="array" ref="M145">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8461,11 +8530,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L146" s="37" t="str" cm="1">
+      <c r="L146" s="30" t="str" cm="1">
         <f t="array" ref="L146">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M146" s="39" t="str" cm="1">
+      <c r="M146" s="32" t="str" cm="1">
         <f t="array" ref="M146">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8505,11 +8574,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L147" s="37" t="str" cm="1">
+      <c r="L147" s="30" t="str" cm="1">
         <f t="array" ref="L147">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M147" s="39" t="str" cm="1">
+      <c r="M147" s="32" t="str" cm="1">
         <f t="array" ref="M147">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8549,11 +8618,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L148" s="37" t="str" cm="1">
+      <c r="L148" s="30" t="str" cm="1">
         <f t="array" ref="L148">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M148" s="39" t="str" cm="1">
+      <c r="M148" s="32" t="str" cm="1">
         <f t="array" ref="M148">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8593,11 +8662,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L149" s="37" t="str" cm="1">
+      <c r="L149" s="30" t="str" cm="1">
         <f t="array" ref="L149">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M149" s="39" t="str" cm="1">
+      <c r="M149" s="32" t="str" cm="1">
         <f t="array" ref="M149">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8637,11 +8706,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L150" s="37" t="str" cm="1">
+      <c r="L150" s="30" t="str" cm="1">
         <f t="array" ref="L150">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M150" s="39" t="str" cm="1">
+      <c r="M150" s="32" t="str" cm="1">
         <f t="array" ref="M150">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8681,11 +8750,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L151" s="37" t="str" cm="1">
+      <c r="L151" s="30" t="str" cm="1">
         <f t="array" ref="L151">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M151" s="39" t="str" cm="1">
+      <c r="M151" s="32" t="str" cm="1">
         <f t="array" ref="M151">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8725,11 +8794,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L152" s="37" t="str" cm="1">
+      <c r="L152" s="30" t="str" cm="1">
         <f t="array" ref="L152">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M152" s="39" t="str" cm="1">
+      <c r="M152" s="32" t="str" cm="1">
         <f t="array" ref="M152">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8769,11 +8838,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L153" s="37" t="str" cm="1">
+      <c r="L153" s="30" t="str" cm="1">
         <f t="array" ref="L153">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M153" s="39" t="str" cm="1">
+      <c r="M153" s="32" t="str" cm="1">
         <f t="array" ref="M153">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8813,11 +8882,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L154" s="37" t="str" cm="1">
+      <c r="L154" s="30" t="str" cm="1">
         <f t="array" ref="L154">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M154" s="39" t="str" cm="1">
+      <c r="M154" s="32" t="str" cm="1">
         <f t="array" ref="M154">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8857,11 +8926,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L155" s="37" t="str" cm="1">
+      <c r="L155" s="30" t="str" cm="1">
         <f t="array" ref="L155">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M155" s="39" t="str" cm="1">
+      <c r="M155" s="32" t="str" cm="1">
         <f t="array" ref="M155">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8901,11 +8970,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L156" s="37" t="str" cm="1">
+      <c r="L156" s="30" t="str" cm="1">
         <f t="array" ref="L156">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M156" s="39" t="str" cm="1">
+      <c r="M156" s="32" t="str" cm="1">
         <f t="array" ref="M156">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -8945,11 +9014,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L157" s="37" t="str" cm="1">
+      <c r="L157" s="30" t="str" cm="1">
         <f t="array" ref="L157">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M157" s="39" t="str" cm="1">
+      <c r="M157" s="32" t="str" cm="1">
         <f t="array" ref="M157">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -8989,11 +9058,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L158" s="37" t="str" cm="1">
+      <c r="L158" s="30" t="str" cm="1">
         <f t="array" ref="L158">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M158" s="39" t="str" cm="1">
+      <c r="M158" s="32" t="str" cm="1">
         <f t="array" ref="M158">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -9033,11 +9102,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L159" s="37" t="str" cm="1">
+      <c r="L159" s="30" t="str" cm="1">
         <f t="array" ref="L159">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M159" s="39" t="str" cm="1">
+      <c r="M159" s="32" t="str" cm="1">
         <f t="array" ref="M159">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9077,11 +9146,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L160" s="37" t="str" cm="1">
+      <c r="L160" s="30" t="str" cm="1">
         <f t="array" ref="L160">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M160" s="39" t="str" cm="1">
+      <c r="M160" s="32" t="str" cm="1">
         <f t="array" ref="M160">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9121,11 +9190,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L161" s="37" t="str" cm="1">
+      <c r="L161" s="30" t="str" cm="1">
         <f t="array" ref="L161">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M161" s="39" t="str" cm="1">
+      <c r="M161" s="32" t="str" cm="1">
         <f t="array" ref="M161">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9165,11 +9234,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L162" s="37" t="str" cm="1">
+      <c r="L162" s="30" t="str" cm="1">
         <f t="array" ref="L162">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M162" s="39" t="str" cm="1">
+      <c r="M162" s="32" t="str" cm="1">
         <f t="array" ref="M162">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9209,11 +9278,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L163" s="37" t="str" cm="1">
+      <c r="L163" s="30" t="str" cm="1">
         <f t="array" ref="L163">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M163" s="39" t="str" cm="1">
+      <c r="M163" s="32" t="str" cm="1">
         <f t="array" ref="M163">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -9253,11 +9322,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L164" s="37" t="str" cm="1">
+      <c r="L164" s="30" t="str" cm="1">
         <f t="array" ref="L164">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M164" s="39" t="str" cm="1">
+      <c r="M164" s="32" t="str" cm="1">
         <f t="array" ref="M164">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9297,11 +9366,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L165" s="37" t="str" cm="1">
+      <c r="L165" s="30" t="str" cm="1">
         <f t="array" ref="L165">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M165" s="39" t="str" cm="1">
+      <c r="M165" s="32" t="str" cm="1">
         <f t="array" ref="M165">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9341,11 +9410,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L166" s="37" t="str" cm="1">
+      <c r="L166" s="30" t="str" cm="1">
         <f t="array" ref="L166">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M166" s="39" t="str" cm="1">
+      <c r="M166" s="32" t="str" cm="1">
         <f t="array" ref="M166">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9385,11 +9454,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L167" s="37" t="str" cm="1">
+      <c r="L167" s="30" t="str" cm="1">
         <f t="array" ref="L167">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M167" s="39" t="str" cm="1">
+      <c r="M167" s="32" t="str" cm="1">
         <f t="array" ref="M167">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -9429,11 +9498,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L168" s="37" t="str" cm="1">
+      <c r="L168" s="30" t="str" cm="1">
         <f t="array" ref="L168">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M168" s="39" t="str" cm="1">
+      <c r="M168" s="32" t="str" cm="1">
         <f t="array" ref="M168">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -9473,11 +9542,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L169" s="37" t="str" cm="1">
+      <c r="L169" s="30" t="str" cm="1">
         <f t="array" ref="L169">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M169" s="39" t="str" cm="1">
+      <c r="M169" s="32" t="str" cm="1">
         <f t="array" ref="M169">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9517,11 +9586,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L170" s="37" t="str" cm="1">
+      <c r="L170" s="30" t="str" cm="1">
         <f t="array" ref="L170">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M170" s="39" t="str" cm="1">
+      <c r="M170" s="32" t="str" cm="1">
         <f t="array" ref="M170">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9561,11 +9630,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L171" s="37" t="str" cm="1">
+      <c r="L171" s="30" t="str" cm="1">
         <f t="array" ref="L171">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M171" s="39" t="str" cm="1">
+      <c r="M171" s="32" t="str" cm="1">
         <f t="array" ref="M171">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9605,11 +9674,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L172" s="37" t="str" cm="1">
+      <c r="L172" s="30" t="str" cm="1">
         <f t="array" ref="L172">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M172" s="39" t="str" cm="1">
+      <c r="M172" s="32" t="str" cm="1">
         <f t="array" ref="M172">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9649,11 +9718,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L173" s="37" t="str" cm="1">
+      <c r="L173" s="30" t="str" cm="1">
         <f t="array" ref="L173">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M173" s="39" t="str" cm="1">
+      <c r="M173" s="32" t="str" cm="1">
         <f t="array" ref="M173">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -9693,11 +9762,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L174" s="37" t="str" cm="1">
+      <c r="L174" s="30" t="str" cm="1">
         <f t="array" ref="L174">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M174" s="39" t="str" cm="1">
+      <c r="M174" s="32" t="str" cm="1">
         <f t="array" ref="M174">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9737,11 +9806,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L175" s="37" t="str" cm="1">
+      <c r="L175" s="30" t="str" cm="1">
         <f t="array" ref="L175">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M175" s="39" t="str" cm="1">
+      <c r="M175" s="32" t="str" cm="1">
         <f t="array" ref="M175">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9781,11 +9850,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L176" s="37" t="str" cm="1">
+      <c r="L176" s="30" t="str" cm="1">
         <f t="array" ref="L176">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M176" s="39" t="str" cm="1">
+      <c r="M176" s="32" t="str" cm="1">
         <f t="array" ref="M176">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -9825,11 +9894,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L177" s="37" t="str" cm="1">
+      <c r="L177" s="30" t="str" cm="1">
         <f t="array" ref="L177">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M177" s="39" t="str" cm="1">
+      <c r="M177" s="32" t="str" cm="1">
         <f t="array" ref="M177">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9869,11 +9938,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L178" s="37" t="str" cm="1">
+      <c r="L178" s="30" t="str" cm="1">
         <f t="array" ref="L178">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M178" s="39" t="str" cm="1">
+      <c r="M178" s="32" t="str" cm="1">
         <f t="array" ref="M178">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -9913,11 +9982,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L179" s="37" t="str" cm="1">
+      <c r="L179" s="30" t="str" cm="1">
         <f t="array" ref="L179">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M179" s="39" t="str" cm="1">
+      <c r="M179" s="32" t="str" cm="1">
         <f t="array" ref="M179">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -9957,11 +10026,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L180" s="37" t="str" cm="1">
+      <c r="L180" s="30" t="str" cm="1">
         <f t="array" ref="L180">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M180" s="39" t="str" cm="1">
+      <c r="M180" s="32" t="str" cm="1">
         <f t="array" ref="M180">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10001,11 +10070,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L181" s="37" t="str" cm="1">
+      <c r="L181" s="30" t="str" cm="1">
         <f t="array" ref="L181">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M181" s="39" t="str" cm="1">
+      <c r="M181" s="32" t="str" cm="1">
         <f t="array" ref="M181">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10045,11 +10114,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L182" s="37" t="str" cm="1">
+      <c r="L182" s="30" t="str" cm="1">
         <f t="array" ref="L182">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M182" s="39" t="str" cm="1">
+      <c r="M182" s="32" t="str" cm="1">
         <f t="array" ref="M182">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10089,11 +10158,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L183" s="37" t="str" cm="1">
+      <c r="L183" s="30" t="str" cm="1">
         <f t="array" ref="L183">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M183" s="39" t="str" cm="1">
+      <c r="M183" s="32" t="str" cm="1">
         <f t="array" ref="M183">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10133,11 +10202,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L184" s="37" t="str" cm="1">
+      <c r="L184" s="30" t="str" cm="1">
         <f t="array" ref="L184">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M184" s="39" t="str" cm="1">
+      <c r="M184" s="32" t="str" cm="1">
         <f t="array" ref="M184">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10177,11 +10246,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L185" s="37" t="str" cm="1">
+      <c r="L185" s="30" t="str" cm="1">
         <f t="array" ref="L185">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M185" s="39" t="str" cm="1">
+      <c r="M185" s="32" t="str" cm="1">
         <f t="array" ref="M185">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10221,11 +10290,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L186" s="37" t="str" cm="1">
+      <c r="L186" s="30" t="str" cm="1">
         <f t="array" ref="L186">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M186" s="39" t="str" cm="1">
+      <c r="M186" s="32" t="str" cm="1">
         <f t="array" ref="M186">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10265,11 +10334,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L187" s="37" t="str" cm="1">
+      <c r="L187" s="30" t="str" cm="1">
         <f t="array" ref="L187">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M187" s="39" t="str" cm="1">
+      <c r="M187" s="32" t="str" cm="1">
         <f t="array" ref="M187">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -10309,11 +10378,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L188" s="37" t="str" cm="1">
+      <c r="L188" s="30" t="str" cm="1">
         <f t="array" ref="L188">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M188" s="39" t="str" cm="1">
+      <c r="M188" s="32" t="str" cm="1">
         <f t="array" ref="M188">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10353,11 +10422,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L189" s="37" t="str" cm="1">
+      <c r="L189" s="30" t="str" cm="1">
         <f t="array" ref="L189">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M189" s="39" t="str" cm="1">
+      <c r="M189" s="32" t="str" cm="1">
         <f t="array" ref="M189">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10397,11 +10466,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L190" s="37" t="str" cm="1">
+      <c r="L190" s="30" t="str" cm="1">
         <f t="array" ref="L190">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M190" s="39" t="str" cm="1">
+      <c r="M190" s="32" t="str" cm="1">
         <f t="array" ref="M190">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -10441,11 +10510,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L191" s="37" t="str" cm="1">
+      <c r="L191" s="30" t="str" cm="1">
         <f t="array" ref="L191">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M191" s="39" t="str" cm="1">
+      <c r="M191" s="32" t="str" cm="1">
         <f t="array" ref="M191">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10485,11 +10554,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L192" s="37" t="str" cm="1">
+      <c r="L192" s="30" t="str" cm="1">
         <f t="array" ref="L192">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M192" s="39" t="str" cm="1">
+      <c r="M192" s="32" t="str" cm="1">
         <f t="array" ref="M192">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -10529,11 +10598,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L193" s="37" t="str" cm="1">
+      <c r="L193" s="30" t="str" cm="1">
         <f t="array" ref="L193">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M193" s="39" t="str" cm="1">
+      <c r="M193" s="32" t="str" cm="1">
         <f t="array" ref="M193">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10573,11 +10642,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L194" s="37" t="str" cm="1">
+      <c r="L194" s="30" t="str" cm="1">
         <f t="array" ref="L194">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M194" s="39" t="str" cm="1">
+      <c r="M194" s="32" t="str" cm="1">
         <f t="array" ref="M194">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10617,11 +10686,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L195" s="37" t="str" cm="1">
+      <c r="L195" s="30" t="str" cm="1">
         <f t="array" ref="L195">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M195" s="39" t="str" cm="1">
+      <c r="M195" s="32" t="str" cm="1">
         <f t="array" ref="M195">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -10661,11 +10730,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L196" s="37" t="str" cm="1">
+      <c r="L196" s="30" t="str" cm="1">
         <f t="array" ref="L196">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M196" s="39" t="str" cm="1">
+      <c r="M196" s="32" t="str" cm="1">
         <f t="array" ref="M196">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -10705,11 +10774,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L197" s="37" t="str" cm="1">
+      <c r="L197" s="30" t="str" cm="1">
         <f t="array" ref="L197">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M197" s="39" t="str" cm="1">
+      <c r="M197" s="32" t="str" cm="1">
         <f t="array" ref="M197">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -10749,11 +10818,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L198" s="37" t="str" cm="1">
+      <c r="L198" s="30" t="str" cm="1">
         <f t="array" ref="L198">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M198" s="39" t="str" cm="1">
+      <c r="M198" s="32" t="str" cm="1">
         <f t="array" ref="M198">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10793,11 +10862,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L199" s="37" t="str" cm="1">
+      <c r="L199" s="30" t="str" cm="1">
         <f t="array" ref="L199">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M199" s="39" t="str" cm="1">
+      <c r="M199" s="32" t="str" cm="1">
         <f t="array" ref="M199">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10837,11 +10906,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L200" s="37" t="str" cm="1">
+      <c r="L200" s="30" t="str" cm="1">
         <f t="array" ref="L200">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M200" s="39" t="str" cm="1">
+      <c r="M200" s="32" t="str" cm="1">
         <f t="array" ref="M200">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10881,11 +10950,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L201" s="37" t="str" cm="1">
+      <c r="L201" s="30" t="str" cm="1">
         <f t="array" ref="L201">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M201" s="39" t="str" cm="1">
+      <c r="M201" s="32" t="str" cm="1">
         <f t="array" ref="M201">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10925,11 +10994,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L202" s="37" t="str" cm="1">
+      <c r="L202" s="30" t="str" cm="1">
         <f t="array" ref="L202">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M202" s="39" t="str" cm="1">
+      <c r="M202" s="32" t="str" cm="1">
         <f t="array" ref="M202">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -10969,11 +11038,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L203" s="37" t="str" cm="1">
+      <c r="L203" s="30" t="str" cm="1">
         <f t="array" ref="L203">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M203" s="39" t="str" cm="1">
+      <c r="M203" s="32" t="str" cm="1">
         <f t="array" ref="M203">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -11013,11 +11082,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L204" s="37" t="str" cm="1">
+      <c r="L204" s="30" t="str" cm="1">
         <f t="array" ref="L204">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M204" s="39" t="str" cm="1">
+      <c r="M204" s="32" t="str" cm="1">
         <f t="array" ref="M204">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11057,11 +11126,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L205" s="37" t="str" cm="1">
+      <c r="L205" s="30" t="str" cm="1">
         <f t="array" ref="L205">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M205" s="39" t="str" cm="1">
+      <c r="M205" s="32" t="str" cm="1">
         <f t="array" ref="M205">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11101,11 +11170,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L206" s="37" t="str" cm="1">
+      <c r="L206" s="30" t="str" cm="1">
         <f t="array" ref="L206">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M206" s="39" t="str" cm="1">
+      <c r="M206" s="32" t="str" cm="1">
         <f t="array" ref="M206">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -11145,11 +11214,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L207" s="37" t="str" cm="1">
+      <c r="L207" s="30" t="str" cm="1">
         <f t="array" ref="L207">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M207" s="39" t="str" cm="1">
+      <c r="M207" s="32" t="str" cm="1">
         <f t="array" ref="M207">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11189,11 +11258,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L208" s="37" t="str" cm="1">
+      <c r="L208" s="30" t="str" cm="1">
         <f t="array" ref="L208">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M208" s="39" t="str" cm="1">
+      <c r="M208" s="32" t="str" cm="1">
         <f t="array" ref="M208">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -11233,11 +11302,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L209" s="37" t="str" cm="1">
+      <c r="L209" s="30" t="str" cm="1">
         <f t="array" ref="L209">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M209" s="39" t="str" cm="1">
+      <c r="M209" s="32" t="str" cm="1">
         <f t="array" ref="M209">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11277,11 +11346,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L210" s="37" t="str" cm="1">
+      <c r="L210" s="30" t="str" cm="1">
         <f t="array" ref="L210">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M210" s="39" t="str" cm="1">
+      <c r="M210" s="32" t="str" cm="1">
         <f t="array" ref="M210">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11321,11 +11390,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L211" s="37" t="str" cm="1">
+      <c r="L211" s="30" t="str" cm="1">
         <f t="array" ref="L211">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M211" s="39" t="str" cm="1">
+      <c r="M211" s="32" t="str" cm="1">
         <f t="array" ref="M211">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -11365,11 +11434,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L212" s="37" t="str" cm="1">
+      <c r="L212" s="30" t="str" cm="1">
         <f t="array" ref="L212">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M212" s="39" t="str" cm="1">
+      <c r="M212" s="32" t="str" cm="1">
         <f t="array" ref="M212">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11409,11 +11478,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L213" s="37" t="str" cm="1">
+      <c r="L213" s="30" t="str" cm="1">
         <f t="array" ref="L213">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M213" s="39" t="str" cm="1">
+      <c r="M213" s="32" t="str" cm="1">
         <f t="array" ref="M213">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -11453,11 +11522,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L214" s="37" t="str" cm="1">
+      <c r="L214" s="30" t="str" cm="1">
         <f t="array" ref="L214">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M214" s="39" t="str" cm="1">
+      <c r="M214" s="32" t="str" cm="1">
         <f t="array" ref="M214">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11497,11 +11566,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L215" s="37" t="str" cm="1">
+      <c r="L215" s="30" t="str" cm="1">
         <f t="array" ref="L215">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M215" s="39" t="str" cm="1">
+      <c r="M215" s="32" t="str" cm="1">
         <f t="array" ref="M215">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -11541,11 +11610,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L216" s="37" t="str" cm="1">
+      <c r="L216" s="30" t="str" cm="1">
         <f t="array" ref="L216">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M216" s="39" t="str" cm="1">
+      <c r="M216" s="32" t="str" cm="1">
         <f t="array" ref="M216">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11585,11 +11654,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L217" s="37" t="str" cm="1">
+      <c r="L217" s="30" t="str" cm="1">
         <f t="array" ref="L217">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M217" s="39" t="str" cm="1">
+      <c r="M217" s="32" t="str" cm="1">
         <f t="array" ref="M217">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11629,11 +11698,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L218" s="37" t="str" cm="1">
+      <c r="L218" s="30" t="str" cm="1">
         <f t="array" ref="L218">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M218" s="39" t="str" cm="1">
+      <c r="M218" s="32" t="str" cm="1">
         <f t="array" ref="M218">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11673,11 +11742,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L219" s="37" t="str" cm="1">
+      <c r="L219" s="30" t="str" cm="1">
         <f t="array" ref="L219">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M219" s="39" t="str" cm="1">
+      <c r="M219" s="32" t="str" cm="1">
         <f t="array" ref="M219">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11717,11 +11786,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L220" s="37" t="str" cm="1">
+      <c r="L220" s="30" t="str" cm="1">
         <f t="array" ref="L220">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M220" s="39" t="str" cm="1">
+      <c r="M220" s="32" t="str" cm="1">
         <f t="array" ref="M220">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -11761,11 +11830,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L221" s="37" t="str" cm="1">
+      <c r="L221" s="30" t="str" cm="1">
         <f t="array" ref="L221">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M221" s="39" t="str" cm="1">
+      <c r="M221" s="32" t="str" cm="1">
         <f t="array" ref="M221">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11805,11 +11874,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L222" s="37" t="str" cm="1">
+      <c r="L222" s="30" t="str" cm="1">
         <f t="array" ref="L222">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M222" s="39" t="str" cm="1">
+      <c r="M222" s="32" t="str" cm="1">
         <f t="array" ref="M222">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11849,11 +11918,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L223" s="37" t="str" cm="1">
+      <c r="L223" s="30" t="str" cm="1">
         <f t="array" ref="L223">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M223" s="39" t="str" cm="1">
+      <c r="M223" s="32" t="str" cm="1">
         <f t="array" ref="M223">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -11893,11 +11962,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L224" s="37" t="str" cm="1">
+      <c r="L224" s="30" t="str" cm="1">
         <f t="array" ref="L224">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M224" s="39" t="str" cm="1">
+      <c r="M224" s="32" t="str" cm="1">
         <f t="array" ref="M224">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11937,11 +12006,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L225" s="37" t="str" cm="1">
+      <c r="L225" s="30" t="str" cm="1">
         <f t="array" ref="L225">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M225" s="39" t="str" cm="1">
+      <c r="M225" s="32" t="str" cm="1">
         <f t="array" ref="M225">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -11981,11 +12050,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L226" s="37" t="str" cm="1">
+      <c r="L226" s="30" t="str" cm="1">
         <f t="array" ref="L226">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M226" s="39" t="str" cm="1">
+      <c r="M226" s="32" t="str" cm="1">
         <f t="array" ref="M226">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12025,11 +12094,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L227" s="37" t="str" cm="1">
+      <c r="L227" s="30" t="str" cm="1">
         <f t="array" ref="L227">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M227" s="39" t="str" cm="1">
+      <c r="M227" s="32" t="str" cm="1">
         <f t="array" ref="M227">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12069,11 +12138,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L228" s="37" t="str" cm="1">
+      <c r="L228" s="30" t="str" cm="1">
         <f t="array" ref="L228">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M228" s="39" t="str" cm="1">
+      <c r="M228" s="32" t="str" cm="1">
         <f t="array" ref="M228">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12113,11 +12182,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L229" s="37" t="str" cm="1">
+      <c r="L229" s="30" t="str" cm="1">
         <f t="array" ref="L229">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M229" s="39" t="str" cm="1">
+      <c r="M229" s="32" t="str" cm="1">
         <f t="array" ref="M229">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12157,11 +12226,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L230" s="37" t="str" cm="1">
+      <c r="L230" s="30" t="str" cm="1">
         <f t="array" ref="L230">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M230" s="39" t="str" cm="1">
+      <c r="M230" s="32" t="str" cm="1">
         <f t="array" ref="M230">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12201,11 +12270,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L231" s="37" t="str" cm="1">
+      <c r="L231" s="30" t="str" cm="1">
         <f t="array" ref="L231">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M231" s="39" t="str" cm="1">
+      <c r="M231" s="32" t="str" cm="1">
         <f t="array" ref="M231">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12245,11 +12314,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L232" s="37" t="str" cm="1">
+      <c r="L232" s="30" t="str" cm="1">
         <f t="array" ref="L232">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M232" s="39" t="str" cm="1">
+      <c r="M232" s="32" t="str" cm="1">
         <f t="array" ref="M232">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12289,11 +12358,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L233" s="37" t="str" cm="1">
+      <c r="L233" s="30" t="str" cm="1">
         <f t="array" ref="L233">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M233" s="39" t="str" cm="1">
+      <c r="M233" s="32" t="str" cm="1">
         <f t="array" ref="M233">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12333,11 +12402,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L234" s="37" t="str" cm="1">
+      <c r="L234" s="30" t="str" cm="1">
         <f t="array" ref="L234">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M234" s="39" t="str" cm="1">
+      <c r="M234" s="32" t="str" cm="1">
         <f t="array" ref="M234">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12377,11 +12446,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L235" s="37" t="str" cm="1">
+      <c r="L235" s="30" t="str" cm="1">
         <f t="array" ref="L235">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M235" s="39" t="str" cm="1">
+      <c r="M235" s="32" t="str" cm="1">
         <f t="array" ref="M235">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12421,11 +12490,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L236" s="37" t="str" cm="1">
+      <c r="L236" s="30" t="str" cm="1">
         <f t="array" ref="L236">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M236" s="39" t="str" cm="1">
+      <c r="M236" s="32" t="str" cm="1">
         <f t="array" ref="M236">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12465,11 +12534,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L237" s="37" t="str" cm="1">
+      <c r="L237" s="30" t="str" cm="1">
         <f t="array" ref="L237">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M237" s="39" t="str" cm="1">
+      <c r="M237" s="32" t="str" cm="1">
         <f t="array" ref="M237">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12509,11 +12578,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L238" s="37" t="str" cm="1">
+      <c r="L238" s="30" t="str" cm="1">
         <f t="array" ref="L238">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M238" s="39" t="str" cm="1">
+      <c r="M238" s="32" t="str" cm="1">
         <f t="array" ref="M238">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12553,11 +12622,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L239" s="37" t="str" cm="1">
+      <c r="L239" s="30" t="str" cm="1">
         <f t="array" ref="L239">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M239" s="39" t="str" cm="1">
+      <c r="M239" s="32" t="str" cm="1">
         <f t="array" ref="M239">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12597,11 +12666,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L240" s="37" t="str" cm="1">
+      <c r="L240" s="30" t="str" cm="1">
         <f t="array" ref="L240">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M240" s="39" t="str" cm="1">
+      <c r="M240" s="32" t="str" cm="1">
         <f t="array" ref="M240">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12641,11 +12710,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L241" s="37" t="str" cm="1">
+      <c r="L241" s="30" t="str" cm="1">
         <f t="array" ref="L241">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M241" s="39" t="str" cm="1">
+      <c r="M241" s="32" t="str" cm="1">
         <f t="array" ref="M241">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -12685,11 +12754,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L242" s="37" t="str" cm="1">
+      <c r="L242" s="30" t="str" cm="1">
         <f t="array" ref="L242">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M242" s="39" t="str" cm="1">
+      <c r="M242" s="32" t="str" cm="1">
         <f t="array" ref="M242">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -12729,11 +12798,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L243" s="37" t="str" cm="1">
+      <c r="L243" s="30" t="str" cm="1">
         <f t="array" ref="L243">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M243" s="39" t="str" cm="1">
+      <c r="M243" s="32" t="str" cm="1">
         <f t="array" ref="M243">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12773,11 +12842,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L244" s="37" t="str" cm="1">
+      <c r="L244" s="30" t="str" cm="1">
         <f t="array" ref="L244">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M244" s="39" t="str" cm="1">
+      <c r="M244" s="32" t="str" cm="1">
         <f t="array" ref="M244">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12817,11 +12886,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L245" s="37" t="str" cm="1">
+      <c r="L245" s="30" t="str" cm="1">
         <f t="array" ref="L245">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M245" s="39" t="str" cm="1">
+      <c r="M245" s="32" t="str" cm="1">
         <f t="array" ref="M245">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12861,11 +12930,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L246" s="37" t="str" cm="1">
+      <c r="L246" s="30" t="str" cm="1">
         <f t="array" ref="L246">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M246" s="39" t="str" cm="1">
+      <c r="M246" s="32" t="str" cm="1">
         <f t="array" ref="M246">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -12905,11 +12974,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L247" s="37" t="str" cm="1">
+      <c r="L247" s="30" t="str" cm="1">
         <f t="array" ref="L247">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M247" s="39" t="str" cm="1">
+      <c r="M247" s="32" t="str" cm="1">
         <f t="array" ref="M247">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12949,11 +13018,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L248" s="37" t="str" cm="1">
+      <c r="L248" s="30" t="str" cm="1">
         <f t="array" ref="L248">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M248" s="39" t="str" cm="1">
+      <c r="M248" s="32" t="str" cm="1">
         <f t="array" ref="M248">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -12993,11 +13062,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L249" s="37" t="str" cm="1">
+      <c r="L249" s="30" t="str" cm="1">
         <f t="array" ref="L249">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M249" s="39" t="str" cm="1">
+      <c r="M249" s="32" t="str" cm="1">
         <f t="array" ref="M249">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13037,11 +13106,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L250" s="37" t="str" cm="1">
+      <c r="L250" s="30" t="str" cm="1">
         <f t="array" ref="L250">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M250" s="39" t="str" cm="1">
+      <c r="M250" s="32" t="str" cm="1">
         <f t="array" ref="M250">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -13081,11 +13150,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L251" s="37" t="str" cm="1">
+      <c r="L251" s="30" t="str" cm="1">
         <f t="array" ref="L251">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M251" s="39" t="str" cm="1">
+      <c r="M251" s="32" t="str" cm="1">
         <f t="array" ref="M251">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13125,11 +13194,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L252" s="37" t="str" cm="1">
+      <c r="L252" s="30" t="str" cm="1">
         <f t="array" ref="L252">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M252" s="39" t="str" cm="1">
+      <c r="M252" s="32" t="str" cm="1">
         <f t="array" ref="M252">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13169,11 +13238,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L253" s="37" t="str" cm="1">
+      <c r="L253" s="30" t="str" cm="1">
         <f t="array" ref="L253">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M253" s="39" t="str" cm="1">
+      <c r="M253" s="32" t="str" cm="1">
         <f t="array" ref="M253">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13213,11 +13282,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L254" s="37" t="str" cm="1">
+      <c r="L254" s="30" t="str" cm="1">
         <f t="array" ref="L254">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M254" s="39" t="str" cm="1">
+      <c r="M254" s="32" t="str" cm="1">
         <f t="array" ref="M254">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13257,11 +13326,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L255" s="37" t="str" cm="1">
+      <c r="L255" s="30" t="str" cm="1">
         <f t="array" ref="L255">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M255" s="39" t="str" cm="1">
+      <c r="M255" s="32" t="str" cm="1">
         <f t="array" ref="M255">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13301,11 +13370,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L256" s="37" t="str" cm="1">
+      <c r="L256" s="30" t="str" cm="1">
         <f t="array" ref="L256">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M256" s="39" t="str" cm="1">
+      <c r="M256" s="32" t="str" cm="1">
         <f t="array" ref="M256">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -13345,11 +13414,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L257" s="37" t="str" cm="1">
+      <c r="L257" s="30" t="str" cm="1">
         <f t="array" ref="L257">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M257" s="39" t="str" cm="1">
+      <c r="M257" s="32" t="str" cm="1">
         <f t="array" ref="M257">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13389,11 +13458,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L258" s="37" t="str" cm="1">
+      <c r="L258" s="30" t="str" cm="1">
         <f t="array" ref="L258">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M258" s="39" t="str" cm="1">
+      <c r="M258" s="32" t="str" cm="1">
         <f t="array" ref="M258">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13433,11 +13502,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L259" s="37" t="str" cm="1">
+      <c r="L259" s="30" t="str" cm="1">
         <f t="array" ref="L259">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M259" s="39" t="str" cm="1">
+      <c r="M259" s="32" t="str" cm="1">
         <f t="array" ref="M259">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -13477,11 +13546,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L260" s="37" t="str" cm="1">
+      <c r="L260" s="30" t="str" cm="1">
         <f t="array" ref="L260">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M260" s="39" t="str" cm="1">
+      <c r="M260" s="32" t="str" cm="1">
         <f t="array" ref="M260">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13521,11 +13590,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L261" s="37" t="str" cm="1">
+      <c r="L261" s="30" t="str" cm="1">
         <f t="array" ref="L261">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M261" s="39" t="str" cm="1">
+      <c r="M261" s="32" t="str" cm="1">
         <f t="array" ref="M261">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13565,11 +13634,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L262" s="37" t="str" cm="1">
+      <c r="L262" s="30" t="str" cm="1">
         <f t="array" ref="L262">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M262" s="39" t="str" cm="1">
+      <c r="M262" s="32" t="str" cm="1">
         <f t="array" ref="M262">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13609,11 +13678,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L263" s="37" t="str" cm="1">
+      <c r="L263" s="30" t="str" cm="1">
         <f t="array" ref="L263">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M263" s="39" t="str" cm="1">
+      <c r="M263" s="32" t="str" cm="1">
         <f t="array" ref="M263">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13653,11 +13722,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L264" s="37" t="str" cm="1">
+      <c r="L264" s="30" t="str" cm="1">
         <f t="array" ref="L264">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M264" s="39" t="str" cm="1">
+      <c r="M264" s="32" t="str" cm="1">
         <f t="array" ref="M264">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -13697,11 +13766,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L265" s="37" t="str" cm="1">
+      <c r="L265" s="30" t="str" cm="1">
         <f t="array" ref="L265">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M265" s="39" t="str" cm="1">
+      <c r="M265" s="32" t="str" cm="1">
         <f t="array" ref="M265">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13741,11 +13810,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L266" s="37" t="str" cm="1">
+      <c r="L266" s="30" t="str" cm="1">
         <f t="array" ref="L266">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M266" s="39" t="str" cm="1">
+      <c r="M266" s="32" t="str" cm="1">
         <f t="array" ref="M266">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13785,11 +13854,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L267" s="37" t="str" cm="1">
+      <c r="L267" s="30" t="str" cm="1">
         <f t="array" ref="L267">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M267" s="39" t="str" cm="1">
+      <c r="M267" s="32" t="str" cm="1">
         <f t="array" ref="M267">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13829,11 +13898,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L268" s="37" t="str" cm="1">
+      <c r="L268" s="30" t="str" cm="1">
         <f t="array" ref="L268">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M268" s="39" t="str" cm="1">
+      <c r="M268" s="32" t="str" cm="1">
         <f t="array" ref="M268">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13873,11 +13942,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L269" s="37" t="str" cm="1">
+      <c r="L269" s="30" t="str" cm="1">
         <f t="array" ref="L269">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M269" s="39" t="str" cm="1">
+      <c r="M269" s="32" t="str" cm="1">
         <f t="array" ref="M269">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -13917,11 +13986,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L270" s="37" t="str" cm="1">
+      <c r="L270" s="30" t="str" cm="1">
         <f t="array" ref="L270">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M270" s="39" t="str" cm="1">
+      <c r="M270" s="32" t="str" cm="1">
         <f t="array" ref="M270">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -13961,11 +14030,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L271" s="37" t="str" cm="1">
+      <c r="L271" s="30" t="str" cm="1">
         <f t="array" ref="L271">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M271" s="39" t="str" cm="1">
+      <c r="M271" s="32" t="str" cm="1">
         <f t="array" ref="M271">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14005,11 +14074,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L272" s="37" t="str" cm="1">
+      <c r="L272" s="30" t="str" cm="1">
         <f t="array" ref="L272">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M272" s="39" t="str" cm="1">
+      <c r="M272" s="32" t="str" cm="1">
         <f t="array" ref="M272">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -14049,11 +14118,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L273" s="37" t="str" cm="1">
+      <c r="L273" s="30" t="str" cm="1">
         <f t="array" ref="L273">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M273" s="39" t="str" cm="1">
+      <c r="M273" s="32" t="str" cm="1">
         <f t="array" ref="M273">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14093,11 +14162,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L274" s="37" t="str" cm="1">
+      <c r="L274" s="30" t="str" cm="1">
         <f t="array" ref="L274">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M274" s="39" t="str" cm="1">
+      <c r="M274" s="32" t="str" cm="1">
         <f t="array" ref="M274">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14137,11 +14206,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L275" s="37" t="str" cm="1">
+      <c r="L275" s="30" t="str" cm="1">
         <f t="array" ref="L275">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M275" s="39" t="str" cm="1">
+      <c r="M275" s="32" t="str" cm="1">
         <f t="array" ref="M275">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -14181,11 +14250,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L276" s="37" t="str" cm="1">
+      <c r="L276" s="30" t="str" cm="1">
         <f t="array" ref="L276">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M276" s="39" t="str" cm="1">
+      <c r="M276" s="32" t="str" cm="1">
         <f t="array" ref="M276">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -14225,11 +14294,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L277" s="37" t="str" cm="1">
+      <c r="L277" s="30" t="str" cm="1">
         <f t="array" ref="L277">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M277" s="39" t="str" cm="1">
+      <c r="M277" s="32" t="str" cm="1">
         <f t="array" ref="M277">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -14269,11 +14338,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L278" s="37" t="str" cm="1">
+      <c r="L278" s="30" t="str" cm="1">
         <f t="array" ref="L278">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M278" s="39" t="str" cm="1">
+      <c r="M278" s="32" t="str" cm="1">
         <f t="array" ref="M278">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14313,11 +14382,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L279" s="37" t="str" cm="1">
+      <c r="L279" s="30" t="str" cm="1">
         <f t="array" ref="L279">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M279" s="39" t="str" cm="1">
+      <c r="M279" s="32" t="str" cm="1">
         <f t="array" ref="M279">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14357,11 +14426,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L280" s="37" t="str" cm="1">
+      <c r="L280" s="30" t="str" cm="1">
         <f t="array" ref="L280">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M280" s="39" t="str" cm="1">
+      <c r="M280" s="32" t="str" cm="1">
         <f t="array" ref="M280">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -14401,11 +14470,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L281" s="37" t="str" cm="1">
+      <c r="L281" s="30" t="str" cm="1">
         <f t="array" ref="L281">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M281" s="39" t="str" cm="1">
+      <c r="M281" s="32" t="str" cm="1">
         <f t="array" ref="M281">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14445,11 +14514,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L282" s="37" t="str" cm="1">
+      <c r="L282" s="30" t="str" cm="1">
         <f t="array" ref="L282">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M282" s="39" t="str" cm="1">
+      <c r="M282" s="32" t="str" cm="1">
         <f t="array" ref="M282">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14489,11 +14558,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L283" s="37" t="str" cm="1">
+      <c r="L283" s="30" t="str" cm="1">
         <f t="array" ref="L283">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M283" s="39" t="str" cm="1">
+      <c r="M283" s="32" t="str" cm="1">
         <f t="array" ref="M283">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14533,11 +14602,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L284" s="37" t="str" cm="1">
+      <c r="L284" s="30" t="str" cm="1">
         <f t="array" ref="L284">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M284" s="39" t="str" cm="1">
+      <c r="M284" s="32" t="str" cm="1">
         <f t="array" ref="M284">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14577,11 +14646,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L285" s="37" t="str" cm="1">
+      <c r="L285" s="30" t="str" cm="1">
         <f t="array" ref="L285">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M285" s="39" t="str" cm="1">
+      <c r="M285" s="32" t="str" cm="1">
         <f t="array" ref="M285">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14621,11 +14690,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L286" s="37" t="str" cm="1">
+      <c r="L286" s="30" t="str" cm="1">
         <f t="array" ref="L286">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M286" s="39" t="str" cm="1">
+      <c r="M286" s="32" t="str" cm="1">
         <f t="array" ref="M286">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -14665,11 +14734,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L287" s="37" t="str" cm="1">
+      <c r="L287" s="30" t="str" cm="1">
         <f t="array" ref="L287">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M287" s="39" t="str" cm="1">
+      <c r="M287" s="32" t="str" cm="1">
         <f t="array" ref="M287">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -14709,11 +14778,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L288" s="37" t="str" cm="1">
+      <c r="L288" s="30" t="str" cm="1">
         <f t="array" ref="L288">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M288" s="39" t="str" cm="1">
+      <c r="M288" s="32" t="str" cm="1">
         <f t="array" ref="M288">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14753,11 +14822,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L289" s="37" t="str" cm="1">
+      <c r="L289" s="30" t="str" cm="1">
         <f t="array" ref="L289">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M289" s="39" t="str" cm="1">
+      <c r="M289" s="32" t="str" cm="1">
         <f t="array" ref="M289">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14797,11 +14866,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L290" s="37" t="str" cm="1">
+      <c r="L290" s="30" t="str" cm="1">
         <f t="array" ref="L290">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M290" s="39" t="str" cm="1">
+      <c r="M290" s="32" t="str" cm="1">
         <f t="array" ref="M290">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14841,11 +14910,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L291" s="37" t="str" cm="1">
+      <c r="L291" s="30" t="str" cm="1">
         <f t="array" ref="L291">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M291" s="39" t="str" cm="1">
+      <c r="M291" s="32" t="str" cm="1">
         <f t="array" ref="M291">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14885,11 +14954,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L292" s="37" t="str" cm="1">
+      <c r="L292" s="30" t="str" cm="1">
         <f t="array" ref="L292">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M292" s="39" t="str" cm="1">
+      <c r="M292" s="32" t="str" cm="1">
         <f t="array" ref="M292">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14929,11 +14998,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L293" s="37" t="str" cm="1">
+      <c r="L293" s="30" t="str" cm="1">
         <f t="array" ref="L293">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M293" s="39" t="str" cm="1">
+      <c r="M293" s="32" t="str" cm="1">
         <f t="array" ref="M293">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -14973,11 +15042,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L294" s="37" t="str" cm="1">
+      <c r="L294" s="30" t="str" cm="1">
         <f t="array" ref="L294">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M294" s="39" t="str" cm="1">
+      <c r="M294" s="32" t="str" cm="1">
         <f t="array" ref="M294">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15017,11 +15086,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L295" s="37" t="str" cm="1">
+      <c r="L295" s="30" t="str" cm="1">
         <f t="array" ref="L295">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M295" s="39" t="str" cm="1">
+      <c r="M295" s="32" t="str" cm="1">
         <f t="array" ref="M295">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -15061,11 +15130,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L296" s="37" t="str" cm="1">
+      <c r="L296" s="30" t="str" cm="1">
         <f t="array" ref="L296">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M296" s="39" t="str" cm="1">
+      <c r="M296" s="32" t="str" cm="1">
         <f t="array" ref="M296">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15105,11 +15174,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L297" s="37" t="str" cm="1">
+      <c r="L297" s="30" t="str" cm="1">
         <f t="array" ref="L297">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M297" s="39" t="str" cm="1">
+      <c r="M297" s="32" t="str" cm="1">
         <f t="array" ref="M297">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15149,11 +15218,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L298" s="37" t="str" cm="1">
+      <c r="L298" s="30" t="str" cm="1">
         <f t="array" ref="L298">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M298" s="39" t="str" cm="1">
+      <c r="M298" s="32" t="str" cm="1">
         <f t="array" ref="M298">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15193,11 +15262,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L299" s="37" t="str" cm="1">
+      <c r="L299" s="30" t="str" cm="1">
         <f t="array" ref="L299">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M299" s="39" t="str" cm="1">
+      <c r="M299" s="32" t="str" cm="1">
         <f t="array" ref="M299">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15237,11 +15306,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L300" s="37" t="str" cm="1">
+      <c r="L300" s="30" t="str" cm="1">
         <f t="array" ref="L300">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M300" s="39" t="str" cm="1">
+      <c r="M300" s="32" t="str" cm="1">
         <f t="array" ref="M300">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15281,11 +15350,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L301" s="37" t="str" cm="1">
+      <c r="L301" s="30" t="str" cm="1">
         <f t="array" ref="L301">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M301" s="39" t="str" cm="1">
+      <c r="M301" s="32" t="str" cm="1">
         <f t="array" ref="M301">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15325,11 +15394,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L302" s="37" t="str" cm="1">
+      <c r="L302" s="30" t="str" cm="1">
         <f t="array" ref="L302">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M302" s="39" t="str" cm="1">
+      <c r="M302" s="32" t="str" cm="1">
         <f t="array" ref="M302">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15369,11 +15438,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L303" s="37" t="str" cm="1">
+      <c r="L303" s="30" t="str" cm="1">
         <f t="array" ref="L303">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M303" s="39" t="str" cm="1">
+      <c r="M303" s="32" t="str" cm="1">
         <f t="array" ref="M303">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -15413,11 +15482,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L304" s="37" t="str" cm="1">
+      <c r="L304" s="30" t="str" cm="1">
         <f t="array" ref="L304">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M304" s="39" t="str" cm="1">
+      <c r="M304" s="32" t="str" cm="1">
         <f t="array" ref="M304">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15457,11 +15526,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L305" s="37" t="str" cm="1">
+      <c r="L305" s="30" t="str" cm="1">
         <f t="array" ref="L305">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M305" s="39" t="str" cm="1">
+      <c r="M305" s="32" t="str" cm="1">
         <f t="array" ref="M305">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15501,11 +15570,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L306" s="37" t="str" cm="1">
+      <c r="L306" s="30" t="str" cm="1">
         <f t="array" ref="L306">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M306" s="39" t="str" cm="1">
+      <c r="M306" s="32" t="str" cm="1">
         <f t="array" ref="M306">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15545,11 +15614,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L307" s="37" t="str" cm="1">
+      <c r="L307" s="30" t="str" cm="1">
         <f t="array" ref="L307">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M307" s="39" t="str" cm="1">
+      <c r="M307" s="32" t="str" cm="1">
         <f t="array" ref="M307">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15589,11 +15658,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L308" s="37" t="str" cm="1">
+      <c r="L308" s="30" t="str" cm="1">
         <f t="array" ref="L308">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M308" s="39" t="str" cm="1">
+      <c r="M308" s="32" t="str" cm="1">
         <f t="array" ref="M308">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15633,11 +15702,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L309" s="37" t="str" cm="1">
+      <c r="L309" s="30" t="str" cm="1">
         <f t="array" ref="L309">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M309" s="39" t="str" cm="1">
+      <c r="M309" s="32" t="str" cm="1">
         <f t="array" ref="M309">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15677,11 +15746,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L310" s="37" t="str" cm="1">
+      <c r="L310" s="30" t="str" cm="1">
         <f t="array" ref="L310">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M310" s="39" t="str" cm="1">
+      <c r="M310" s="32" t="str" cm="1">
         <f t="array" ref="M310">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15721,11 +15790,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L311" s="37" t="str" cm="1">
+      <c r="L311" s="30" t="str" cm="1">
         <f t="array" ref="L311">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M311" s="39" t="str" cm="1">
+      <c r="M311" s="32" t="str" cm="1">
         <f t="array" ref="M311">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15765,11 +15834,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L312" s="37" t="str" cm="1">
+      <c r="L312" s="30" t="str" cm="1">
         <f t="array" ref="L312">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M312" s="39" t="str" cm="1">
+      <c r="M312" s="32" t="str" cm="1">
         <f t="array" ref="M312">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15809,11 +15878,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L313" s="37" t="str" cm="1">
+      <c r="L313" s="30" t="str" cm="1">
         <f t="array" ref="L313">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M313" s="39" t="str" cm="1">
+      <c r="M313" s="32" t="str" cm="1">
         <f t="array" ref="M313">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15853,11 +15922,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L314" s="37" t="str" cm="1">
+      <c r="L314" s="30" t="str" cm="1">
         <f t="array" ref="L314">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M314" s="39" t="str" cm="1">
+      <c r="M314" s="32" t="str" cm="1">
         <f t="array" ref="M314">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -15897,11 +15966,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L315" s="37" t="str" cm="1">
+      <c r="L315" s="30" t="str" cm="1">
         <f t="array" ref="L315">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M315" s="39" t="str" cm="1">
+      <c r="M315" s="32" t="str" cm="1">
         <f t="array" ref="M315">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -15941,11 +16010,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L316" s="37" t="str" cm="1">
+      <c r="L316" s="30" t="str" cm="1">
         <f t="array" ref="L316">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M316" s="39" t="str" cm="1">
+      <c r="M316" s="32" t="str" cm="1">
         <f t="array" ref="M316">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -15985,11 +16054,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L317" s="37" t="str" cm="1">
+      <c r="L317" s="30" t="str" cm="1">
         <f t="array" ref="L317">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M317" s="39" t="str" cm="1">
+      <c r="M317" s="32" t="str" cm="1">
         <f t="array" ref="M317">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16029,11 +16098,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L318" s="37" t="str" cm="1">
+      <c r="L318" s="30" t="str" cm="1">
         <f t="array" ref="L318">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M318" s="39" t="str" cm="1">
+      <c r="M318" s="32" t="str" cm="1">
         <f t="array" ref="M318">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16073,11 +16142,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L319" s="37" t="str" cm="1">
+      <c r="L319" s="30" t="str" cm="1">
         <f t="array" ref="L319">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M319" s="39" t="str" cm="1">
+      <c r="M319" s="32" t="str" cm="1">
         <f t="array" ref="M319">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16117,11 +16186,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L320" s="37" t="str" cm="1">
+      <c r="L320" s="30" t="str" cm="1">
         <f t="array" ref="L320">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M320" s="39" t="str" cm="1">
+      <c r="M320" s="32" t="str" cm="1">
         <f t="array" ref="M320">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16161,11 +16230,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L321" s="37" t="str" cm="1">
+      <c r="L321" s="30" t="str" cm="1">
         <f t="array" ref="L321">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M321" s="39" t="str" cm="1">
+      <c r="M321" s="32" t="str" cm="1">
         <f t="array" ref="M321">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16205,11 +16274,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L322" s="37" t="str" cm="1">
+      <c r="L322" s="30" t="str" cm="1">
         <f t="array" ref="L322">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M322" s="39" t="str" cm="1">
+      <c r="M322" s="32" t="str" cm="1">
         <f t="array" ref="M322">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16249,11 +16318,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L323" s="37" t="str" cm="1">
+      <c r="L323" s="30" t="str" cm="1">
         <f t="array" ref="L323">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M323" s="39" t="str" cm="1">
+      <c r="M323" s="32" t="str" cm="1">
         <f t="array" ref="M323">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16293,11 +16362,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L324" s="37" t="str" cm="1">
+      <c r="L324" s="30" t="str" cm="1">
         <f t="array" ref="L324">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M324" s="39" t="str" cm="1">
+      <c r="M324" s="32" t="str" cm="1">
         <f t="array" ref="M324">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16337,11 +16406,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L325" s="37" t="str" cm="1">
+      <c r="L325" s="30" t="str" cm="1">
         <f t="array" ref="L325">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M325" s="39" t="str" cm="1">
+      <c r="M325" s="32" t="str" cm="1">
         <f t="array" ref="M325">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16381,11 +16450,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L326" s="37" t="str" cm="1">
+      <c r="L326" s="30" t="str" cm="1">
         <f t="array" ref="L326">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M326" s="39" t="str" cm="1">
+      <c r="M326" s="32" t="str" cm="1">
         <f t="array" ref="M326">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16425,11 +16494,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L327" s="37" t="str" cm="1">
+      <c r="L327" s="30" t="str" cm="1">
         <f t="array" ref="L327">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M327" s="39" t="str" cm="1">
+      <c r="M327" s="32" t="str" cm="1">
         <f t="array" ref="M327">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16469,11 +16538,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L328" s="37" t="str" cm="1">
+      <c r="L328" s="30" t="str" cm="1">
         <f t="array" ref="L328">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M328" s="39" t="str" cm="1">
+      <c r="M328" s="32" t="str" cm="1">
         <f t="array" ref="M328">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16513,11 +16582,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L329" s="37" t="str" cm="1">
+      <c r="L329" s="30" t="str" cm="1">
         <f t="array" ref="L329">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M329" s="39" t="str" cm="1">
+      <c r="M329" s="32" t="str" cm="1">
         <f t="array" ref="M329">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16557,11 +16626,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L330" s="37" t="str" cm="1">
+      <c r="L330" s="30" t="str" cm="1">
         <f t="array" ref="L330">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M330" s="39" t="str" cm="1">
+      <c r="M330" s="32" t="str" cm="1">
         <f t="array" ref="M330">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16601,11 +16670,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L331" s="37" t="str" cm="1">
+      <c r="L331" s="30" t="str" cm="1">
         <f t="array" ref="L331">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M331" s="39" t="str" cm="1">
+      <c r="M331" s="32" t="str" cm="1">
         <f t="array" ref="M331">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16645,11 +16714,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L332" s="37" t="str" cm="1">
+      <c r="L332" s="30" t="str" cm="1">
         <f t="array" ref="L332">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M332" s="39" t="str" cm="1">
+      <c r="M332" s="32" t="str" cm="1">
         <f t="array" ref="M332">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16689,11 +16758,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L333" s="37" t="str" cm="1">
+      <c r="L333" s="30" t="str" cm="1">
         <f t="array" ref="L333">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M333" s="39" t="str" cm="1">
+      <c r="M333" s="32" t="str" cm="1">
         <f t="array" ref="M333">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16733,11 +16802,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L334" s="37" t="str" cm="1">
+      <c r="L334" s="30" t="str" cm="1">
         <f t="array" ref="L334">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M334" s="39" t="str" cm="1">
+      <c r="M334" s="32" t="str" cm="1">
         <f t="array" ref="M334">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16777,11 +16846,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L335" s="37" t="str" cm="1">
+      <c r="L335" s="30" t="str" cm="1">
         <f t="array" ref="L335">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M335" s="39" t="str" cm="1">
+      <c r="M335" s="32" t="str" cm="1">
         <f t="array" ref="M335">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16821,11 +16890,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L336" s="37" t="str" cm="1">
+      <c r="L336" s="30" t="str" cm="1">
         <f t="array" ref="L336">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M336" s="39" t="str" cm="1">
+      <c r="M336" s="32" t="str" cm="1">
         <f t="array" ref="M336">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16865,11 +16934,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L337" s="37" t="str" cm="1">
+      <c r="L337" s="30" t="str" cm="1">
         <f t="array" ref="L337">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M337" s="39" t="str" cm="1">
+      <c r="M337" s="32" t="str" cm="1">
         <f t="array" ref="M337">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16909,11 +16978,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L338" s="37" t="str" cm="1">
+      <c r="L338" s="30" t="str" cm="1">
         <f t="array" ref="L338">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M338" s="39" t="str" cm="1">
+      <c r="M338" s="32" t="str" cm="1">
         <f t="array" ref="M338">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -16953,11 +17022,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L339" s="37" t="str" cm="1">
+      <c r="L339" s="30" t="str" cm="1">
         <f t="array" ref="L339">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M339" s="39" t="str" cm="1">
+      <c r="M339" s="32" t="str" cm="1">
         <f t="array" ref="M339">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -16997,11 +17066,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L340" s="37" t="str" cm="1">
+      <c r="L340" s="30" t="str" cm="1">
         <f t="array" ref="L340">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M340" s="39" t="str" cm="1">
+      <c r="M340" s="32" t="str" cm="1">
         <f t="array" ref="M340">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17041,11 +17110,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L341" s="37" t="str" cm="1">
+      <c r="L341" s="30" t="str" cm="1">
         <f t="array" ref="L341">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M341" s="39" t="str" cm="1">
+      <c r="M341" s="32" t="str" cm="1">
         <f t="array" ref="M341">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17085,11 +17154,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L342" s="37" t="str" cm="1">
+      <c r="L342" s="30" t="str" cm="1">
         <f t="array" ref="L342">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M342" s="39" t="str" cm="1">
+      <c r="M342" s="32" t="str" cm="1">
         <f t="array" ref="M342">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17129,11 +17198,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L343" s="37" t="str" cm="1">
+      <c r="L343" s="30" t="str" cm="1">
         <f t="array" ref="L343">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M343" s="39" t="str" cm="1">
+      <c r="M343" s="32" t="str" cm="1">
         <f t="array" ref="M343">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17173,11 +17242,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L344" s="37" t="str" cm="1">
+      <c r="L344" s="30" t="str" cm="1">
         <f t="array" ref="L344">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M344" s="39" t="str" cm="1">
+      <c r="M344" s="32" t="str" cm="1">
         <f t="array" ref="M344">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17217,11 +17286,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L345" s="37" t="str" cm="1">
+      <c r="L345" s="30" t="str" cm="1">
         <f t="array" ref="L345">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M345" s="39" t="str" cm="1">
+      <c r="M345" s="32" t="str" cm="1">
         <f t="array" ref="M345">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -17261,11 +17330,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L346" s="37" t="str" cm="1">
+      <c r="L346" s="30" t="str" cm="1">
         <f t="array" ref="L346">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M346" s="39" t="str" cm="1">
+      <c r="M346" s="32" t="str" cm="1">
         <f t="array" ref="M346">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17305,11 +17374,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L347" s="37" t="str" cm="1">
+      <c r="L347" s="30" t="str" cm="1">
         <f t="array" ref="L347">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M347" s="39" t="str" cm="1">
+      <c r="M347" s="32" t="str" cm="1">
         <f t="array" ref="M347">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -17349,11 +17418,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L348" s="37" t="str" cm="1">
+      <c r="L348" s="30" t="str" cm="1">
         <f t="array" ref="L348">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M348" s="39" t="str" cm="1">
+      <c r="M348" s="32" t="str" cm="1">
         <f t="array" ref="M348">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17393,11 +17462,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L349" s="37" t="str" cm="1">
+      <c r="L349" s="30" t="str" cm="1">
         <f t="array" ref="L349">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M349" s="39" t="str" cm="1">
+      <c r="M349" s="32" t="str" cm="1">
         <f t="array" ref="M349">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17437,11 +17506,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L350" s="37" t="str" cm="1">
+      <c r="L350" s="30" t="str" cm="1">
         <f t="array" ref="L350">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M350" s="39" t="str" cm="1">
+      <c r="M350" s="32" t="str" cm="1">
         <f t="array" ref="M350">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17481,11 +17550,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L351" s="37" t="str" cm="1">
+      <c r="L351" s="30" t="str" cm="1">
         <f t="array" ref="L351">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M351" s="39" t="str" cm="1">
+      <c r="M351" s="32" t="str" cm="1">
         <f t="array" ref="M351">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17525,11 +17594,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L352" s="37" t="str" cm="1">
+      <c r="L352" s="30" t="str" cm="1">
         <f t="array" ref="L352">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M352" s="39" t="str" cm="1">
+      <c r="M352" s="32" t="str" cm="1">
         <f t="array" ref="M352">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17569,11 +17638,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L353" s="37" t="str" cm="1">
+      <c r="L353" s="30" t="str" cm="1">
         <f t="array" ref="L353">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M353" s="39" t="str" cm="1">
+      <c r="M353" s="32" t="str" cm="1">
         <f t="array" ref="M353">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -17613,11 +17682,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L354" s="37" t="str" cm="1">
+      <c r="L354" s="30" t="str" cm="1">
         <f t="array" ref="L354">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M354" s="39" t="str" cm="1">
+      <c r="M354" s="32" t="str" cm="1">
         <f t="array" ref="M354">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17657,11 +17726,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L355" s="37" t="str" cm="1">
+      <c r="L355" s="30" t="str" cm="1">
         <f t="array" ref="L355">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M355" s="39" t="str" cm="1">
+      <c r="M355" s="32" t="str" cm="1">
         <f t="array" ref="M355">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -17701,11 +17770,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L356" s="37" t="str" cm="1">
+      <c r="L356" s="30" t="str" cm="1">
         <f t="array" ref="L356">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M356" s="39" t="str" cm="1">
+      <c r="M356" s="32" t="str" cm="1">
         <f t="array" ref="M356">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -17745,11 +17814,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L357" s="37" t="str" cm="1">
+      <c r="L357" s="30" t="str" cm="1">
         <f t="array" ref="L357">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M357" s="39" t="str" cm="1">
+      <c r="M357" s="32" t="str" cm="1">
         <f t="array" ref="M357">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17789,11 +17858,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L358" s="37" t="str" cm="1">
+      <c r="L358" s="30" t="str" cm="1">
         <f t="array" ref="L358">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M358" s="39" t="str" cm="1">
+      <c r="M358" s="32" t="str" cm="1">
         <f t="array" ref="M358">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17833,11 +17902,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L359" s="37" t="str" cm="1">
+      <c r="L359" s="30" t="str" cm="1">
         <f t="array" ref="L359">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M359" s="39" t="str" cm="1">
+      <c r="M359" s="32" t="str" cm="1">
         <f t="array" ref="M359">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -17877,11 +17946,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L360" s="37" t="str" cm="1">
+      <c r="L360" s="30" t="str" cm="1">
         <f t="array" ref="L360">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M360" s="39" t="str" cm="1">
+      <c r="M360" s="32" t="str" cm="1">
         <f t="array" ref="M360">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -17921,11 +17990,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L361" s="37" t="str" cm="1">
+      <c r="L361" s="30" t="str" cm="1">
         <f t="array" ref="L361">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M361" s="39" t="str" cm="1">
+      <c r="M361" s="32" t="str" cm="1">
         <f t="array" ref="M361">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -17965,11 +18034,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L362" s="37" t="str" cm="1">
+      <c r="L362" s="30" t="str" cm="1">
         <f t="array" ref="L362">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M362" s="39" t="str" cm="1">
+      <c r="M362" s="32" t="str" cm="1">
         <f t="array" ref="M362">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18009,11 +18078,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L363" s="37" t="str" cm="1">
+      <c r="L363" s="30" t="str" cm="1">
         <f t="array" ref="L363">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M363" s="39" t="str" cm="1">
+      <c r="M363" s="32" t="str" cm="1">
         <f t="array" ref="M363">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18053,11 +18122,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L364" s="37" t="str" cm="1">
+      <c r="L364" s="30" t="str" cm="1">
         <f t="array" ref="L364">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M364" s="39" t="str" cm="1">
+      <c r="M364" s="32" t="str" cm="1">
         <f t="array" ref="M364">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18097,11 +18166,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L365" s="37" t="str" cm="1">
+      <c r="L365" s="30" t="str" cm="1">
         <f t="array" ref="L365">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M365" s="39" t="str" cm="1">
+      <c r="M365" s="32" t="str" cm="1">
         <f t="array" ref="M365">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18141,11 +18210,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L366" s="37" t="str" cm="1">
+      <c r="L366" s="30" t="str" cm="1">
         <f t="array" ref="L366">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M366" s="39" t="str" cm="1">
+      <c r="M366" s="32" t="str" cm="1">
         <f t="array" ref="M366">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -18185,11 +18254,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L367" s="37" t="str" cm="1">
+      <c r="L367" s="30" t="str" cm="1">
         <f t="array" ref="L367">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M367" s="39" t="str" cm="1">
+      <c r="M367" s="32" t="str" cm="1">
         <f t="array" ref="M367">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18229,11 +18298,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L368" s="37" t="str" cm="1">
+      <c r="L368" s="30" t="str" cm="1">
         <f t="array" ref="L368">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M368" s="39" t="str" cm="1">
+      <c r="M368" s="32" t="str" cm="1">
         <f t="array" ref="M368">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18273,11 +18342,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L369" s="37" t="str" cm="1">
+      <c r="L369" s="30" t="str" cm="1">
         <f t="array" ref="L369">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M369" s="39" t="str" cm="1">
+      <c r="M369" s="32" t="str" cm="1">
         <f t="array" ref="M369">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18317,11 +18386,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L370" s="37" t="str" cm="1">
+      <c r="L370" s="30" t="str" cm="1">
         <f t="array" ref="L370">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M370" s="39" t="str" cm="1">
+      <c r="M370" s="32" t="str" cm="1">
         <f t="array" ref="M370">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18361,11 +18430,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L371" s="37" t="str" cm="1">
+      <c r="L371" s="30" t="str" cm="1">
         <f t="array" ref="L371">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M371" s="39" t="str" cm="1">
+      <c r="M371" s="32" t="str" cm="1">
         <f t="array" ref="M371">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18405,11 +18474,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L372" s="37" t="str" cm="1">
+      <c r="L372" s="30" t="str" cm="1">
         <f t="array" ref="L372">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M372" s="39" t="str" cm="1">
+      <c r="M372" s="32" t="str" cm="1">
         <f t="array" ref="M372">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18449,11 +18518,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L373" s="37" t="str" cm="1">
+      <c r="L373" s="30" t="str" cm="1">
         <f t="array" ref="L373">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M373" s="39" t="str" cm="1">
+      <c r="M373" s="32" t="str" cm="1">
         <f t="array" ref="M373">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18493,11 +18562,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L374" s="37" t="str" cm="1">
+      <c r="L374" s="30" t="str" cm="1">
         <f t="array" ref="L374">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M374" s="39" t="str" cm="1">
+      <c r="M374" s="32" t="str" cm="1">
         <f t="array" ref="M374">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18537,11 +18606,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L375" s="37" t="str" cm="1">
+      <c r="L375" s="30" t="str" cm="1">
         <f t="array" ref="L375">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M375" s="39" t="str" cm="1">
+      <c r="M375" s="32" t="str" cm="1">
         <f t="array" ref="M375">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18581,11 +18650,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L376" s="37" t="str" cm="1">
+      <c r="L376" s="30" t="str" cm="1">
         <f t="array" ref="L376">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M376" s="39" t="str" cm="1">
+      <c r="M376" s="32" t="str" cm="1">
         <f t="array" ref="M376">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18625,11 +18694,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L377" s="37" t="str" cm="1">
+      <c r="L377" s="30" t="str" cm="1">
         <f t="array" ref="L377">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M377" s="39" t="str" cm="1">
+      <c r="M377" s="32" t="str" cm="1">
         <f t="array" ref="M377">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18669,11 +18738,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L378" s="37" t="str" cm="1">
+      <c r="L378" s="30" t="str" cm="1">
         <f t="array" ref="L378">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M378" s="39" t="str" cm="1">
+      <c r="M378" s="32" t="str" cm="1">
         <f t="array" ref="M378">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18713,11 +18782,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L379" s="37" t="str" cm="1">
+      <c r="L379" s="30" t="str" cm="1">
         <f t="array" ref="L379">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M379" s="39" t="str" cm="1">
+      <c r="M379" s="32" t="str" cm="1">
         <f t="array" ref="M379">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18757,11 +18826,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L380" s="37" t="str" cm="1">
+      <c r="L380" s="30" t="str" cm="1">
         <f t="array" ref="L380">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M380" s="39" t="str" cm="1">
+      <c r="M380" s="32" t="str" cm="1">
         <f t="array" ref="M380">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18801,11 +18870,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L381" s="37" t="str" cm="1">
+      <c r="L381" s="30" t="str" cm="1">
         <f t="array" ref="L381">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M381" s="39" t="str" cm="1">
+      <c r="M381" s="32" t="str" cm="1">
         <f t="array" ref="M381">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18845,11 +18914,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L382" s="37" t="str" cm="1">
+      <c r="L382" s="30" t="str" cm="1">
         <f t="array" ref="L382">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M382" s="39" t="str" cm="1">
+      <c r="M382" s="32" t="str" cm="1">
         <f t="array" ref="M382">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18889,11 +18958,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L383" s="37" t="str" cm="1">
+      <c r="L383" s="30" t="str" cm="1">
         <f t="array" ref="L383">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M383" s="39" t="str" cm="1">
+      <c r="M383" s="32" t="str" cm="1">
         <f t="array" ref="M383">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -18933,11 +19002,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L384" s="37" t="str" cm="1">
+      <c r="L384" s="30" t="str" cm="1">
         <f t="array" ref="L384">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M384" s="39" t="str" cm="1">
+      <c r="M384" s="32" t="str" cm="1">
         <f t="array" ref="M384">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -18977,11 +19046,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L385" s="37" t="str" cm="1">
+      <c r="L385" s="30" t="str" cm="1">
         <f t="array" ref="L385">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M385" s="39" t="str" cm="1">
+      <c r="M385" s="32" t="str" cm="1">
         <f t="array" ref="M385">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19021,11 +19090,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L386" s="37" t="str" cm="1">
+      <c r="L386" s="30" t="str" cm="1">
         <f t="array" ref="L386">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M386" s="39" t="str" cm="1">
+      <c r="M386" s="32" t="str" cm="1">
         <f t="array" ref="M386">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19065,11 +19134,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L387" s="37" t="str" cm="1">
+      <c r="L387" s="30" t="str" cm="1">
         <f t="array" ref="L387">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M387" s="39" t="str" cm="1">
+      <c r="M387" s="32" t="str" cm="1">
         <f t="array" ref="M387">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19109,11 +19178,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L388" s="37" t="str" cm="1">
+      <c r="L388" s="30" t="str" cm="1">
         <f t="array" ref="L388">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M388" s="39" t="str" cm="1">
+      <c r="M388" s="32" t="str" cm="1">
         <f t="array" ref="M388">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19153,11 +19222,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L389" s="37" t="str" cm="1">
+      <c r="L389" s="30" t="str" cm="1">
         <f t="array" ref="L389">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M389" s="39" t="str" cm="1">
+      <c r="M389" s="32" t="str" cm="1">
         <f t="array" ref="M389">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -19197,11 +19266,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L390" s="37" t="str" cm="1">
+      <c r="L390" s="30" t="str" cm="1">
         <f t="array" ref="L390">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M390" s="39" t="str" cm="1">
+      <c r="M390" s="32" t="str" cm="1">
         <f t="array" ref="M390">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -19241,11 +19310,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L391" s="37" t="str" cm="1">
+      <c r="L391" s="30" t="str" cm="1">
         <f t="array" ref="L391">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M391" s="39" t="str" cm="1">
+      <c r="M391" s="32" t="str" cm="1">
         <f t="array" ref="M391">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19285,11 +19354,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L392" s="37" t="str" cm="1">
+      <c r="L392" s="30" t="str" cm="1">
         <f t="array" ref="L392">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M392" s="39" t="str" cm="1">
+      <c r="M392" s="32" t="str" cm="1">
         <f t="array" ref="M392">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19329,11 +19398,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L393" s="37" t="str" cm="1">
+      <c r="L393" s="30" t="str" cm="1">
         <f t="array" ref="L393">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M393" s="39" t="str" cm="1">
+      <c r="M393" s="32" t="str" cm="1">
         <f t="array" ref="M393">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19373,11 +19442,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L394" s="37" t="str" cm="1">
+      <c r="L394" s="30" t="str" cm="1">
         <f t="array" ref="L394">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M394" s="39" t="str" cm="1">
+      <c r="M394" s="32" t="str" cm="1">
         <f t="array" ref="M394">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19417,11 +19486,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L395" s="37" t="str" cm="1">
+      <c r="L395" s="30" t="str" cm="1">
         <f t="array" ref="L395">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M395" s="39" t="str" cm="1">
+      <c r="M395" s="32" t="str" cm="1">
         <f t="array" ref="M395">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19461,11 +19530,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L396" s="37" t="str" cm="1">
+      <c r="L396" s="30" t="str" cm="1">
         <f t="array" ref="L396">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M396" s="39" t="str" cm="1">
+      <c r="M396" s="32" t="str" cm="1">
         <f t="array" ref="M396">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19505,11 +19574,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L397" s="37" t="str" cm="1">
+      <c r="L397" s="30" t="str" cm="1">
         <f t="array" ref="L397">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M397" s="39" t="str" cm="1">
+      <c r="M397" s="32" t="str" cm="1">
         <f t="array" ref="M397">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19549,11 +19618,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L398" s="37" t="str" cm="1">
+      <c r="L398" s="30" t="str" cm="1">
         <f t="array" ref="L398">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M398" s="39" t="str" cm="1">
+      <c r="M398" s="32" t="str" cm="1">
         <f t="array" ref="M398">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19593,11 +19662,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L399" s="37" t="str" cm="1">
+      <c r="L399" s="30" t="str" cm="1">
         <f t="array" ref="L399">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M399" s="39" t="str" cm="1">
+      <c r="M399" s="32" t="str" cm="1">
         <f t="array" ref="M399">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19637,11 +19706,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L400" s="37" t="str" cm="1">
+      <c r="L400" s="30" t="str" cm="1">
         <f t="array" ref="L400">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M400" s="39" t="str" cm="1">
+      <c r="M400" s="32" t="str" cm="1">
         <f t="array" ref="M400">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19681,11 +19750,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L401" s="37" t="str" cm="1">
+      <c r="L401" s="30" t="str" cm="1">
         <f t="array" ref="L401">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M401" s="39" t="str" cm="1">
+      <c r="M401" s="32" t="str" cm="1">
         <f t="array" ref="M401">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19725,11 +19794,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L402" s="37" t="str" cm="1">
+      <c r="L402" s="30" t="str" cm="1">
         <f t="array" ref="L402">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M402" s="39" t="str" cm="1">
+      <c r="M402" s="32" t="str" cm="1">
         <f t="array" ref="M402">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19769,11 +19838,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L403" s="37" t="str" cm="1">
+      <c r="L403" s="30" t="str" cm="1">
         <f t="array" ref="L403">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M403" s="39" t="str" cm="1">
+      <c r="M403" s="32" t="str" cm="1">
         <f t="array" ref="M403">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -19813,11 +19882,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L404" s="37" t="str" cm="1">
+      <c r="L404" s="30" t="str" cm="1">
         <f t="array" ref="L404">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M404" s="39" t="str" cm="1">
+      <c r="M404" s="32" t="str" cm="1">
         <f t="array" ref="M404">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -19857,11 +19926,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L405" s="37" t="str" cm="1">
+      <c r="L405" s="30" t="str" cm="1">
         <f t="array" ref="L405">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M405" s="39" t="str" cm="1">
+      <c r="M405" s="32" t="str" cm="1">
         <f t="array" ref="M405">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19901,11 +19970,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L406" s="37" t="str" cm="1">
+      <c r="L406" s="30" t="str" cm="1">
         <f t="array" ref="L406">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M406" s="39" t="str" cm="1">
+      <c r="M406" s="32" t="str" cm="1">
         <f t="array" ref="M406">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19945,11 +20014,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L407" s="37" t="str" cm="1">
+      <c r="L407" s="30" t="str" cm="1">
         <f t="array" ref="L407">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M407" s="39" t="str" cm="1">
+      <c r="M407" s="32" t="str" cm="1">
         <f t="array" ref="M407">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -19989,11 +20058,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L408" s="37" t="str" cm="1">
+      <c r="L408" s="30" t="str" cm="1">
         <f t="array" ref="L408">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M408" s="39" t="str" cm="1">
+      <c r="M408" s="32" t="str" cm="1">
         <f t="array" ref="M408">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -20033,11 +20102,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L409" s="37" t="str" cm="1">
+      <c r="L409" s="30" t="str" cm="1">
         <f t="array" ref="L409">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M409" s="39" t="str" cm="1">
+      <c r="M409" s="32" t="str" cm="1">
         <f t="array" ref="M409">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -20077,11 +20146,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L410" s="37" t="str" cm="1">
+      <c r="L410" s="30" t="str" cm="1">
         <f t="array" ref="L410">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M410" s="39" t="str" cm="1">
+      <c r="M410" s="32" t="str" cm="1">
         <f t="array" ref="M410">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20121,11 +20190,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L411" s="37" t="str" cm="1">
+      <c r="L411" s="30" t="str" cm="1">
         <f t="array" ref="L411">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M411" s="39" t="str" cm="1">
+      <c r="M411" s="32" t="str" cm="1">
         <f t="array" ref="M411">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -20165,11 +20234,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L412" s="37" t="str" cm="1">
+      <c r="L412" s="30" t="str" cm="1">
         <f t="array" ref="L412">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M412" s="39" t="str" cm="1">
+      <c r="M412" s="32" t="str" cm="1">
         <f t="array" ref="M412">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20209,11 +20278,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L413" s="37" t="str" cm="1">
+      <c r="L413" s="30" t="str" cm="1">
         <f t="array" ref="L413">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M413" s="39" t="str" cm="1">
+      <c r="M413" s="32" t="str" cm="1">
         <f t="array" ref="M413">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20253,11 +20322,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L414" s="37" t="str" cm="1">
+      <c r="L414" s="30" t="str" cm="1">
         <f t="array" ref="L414">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M414" s="39" t="str" cm="1">
+      <c r="M414" s="32" t="str" cm="1">
         <f t="array" ref="M414">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20297,11 +20366,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L415" s="37" t="str" cm="1">
+      <c r="L415" s="30" t="str" cm="1">
         <f t="array" ref="L415">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M415" s="39" t="str" cm="1">
+      <c r="M415" s="32" t="str" cm="1">
         <f t="array" ref="M415">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -20341,11 +20410,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L416" s="37" t="str" cm="1">
+      <c r="L416" s="30" t="str" cm="1">
         <f t="array" ref="L416">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M416" s="39" t="str" cm="1">
+      <c r="M416" s="32" t="str" cm="1">
         <f t="array" ref="M416">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -20385,11 +20454,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L417" s="37" t="str" cm="1">
+      <c r="L417" s="30" t="str" cm="1">
         <f t="array" ref="L417">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M417" s="39" t="str" cm="1">
+      <c r="M417" s="32" t="str" cm="1">
         <f t="array" ref="M417">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20429,11 +20498,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L418" s="37" t="str" cm="1">
+      <c r="L418" s="30" t="str" cm="1">
         <f t="array" ref="L418">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M418" s="39" t="str" cm="1">
+      <c r="M418" s="32" t="str" cm="1">
         <f t="array" ref="M418">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -20473,11 +20542,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L419" s="37" t="str" cm="1">
+      <c r="L419" s="30" t="str" cm="1">
         <f t="array" ref="L419">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M419" s="39" t="str" cm="1">
+      <c r="M419" s="32" t="str" cm="1">
         <f t="array" ref="M419">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -20517,11 +20586,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L420" s="37" t="str" cm="1">
+      <c r="L420" s="30" t="str" cm="1">
         <f t="array" ref="L420">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M420" s="39" t="str" cm="1">
+      <c r="M420" s="32" t="str" cm="1">
         <f t="array" ref="M420">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20561,11 +20630,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L421" s="37" t="str" cm="1">
+      <c r="L421" s="30" t="str" cm="1">
         <f t="array" ref="L421">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M421" s="39" t="str" cm="1">
+      <c r="M421" s="32" t="str" cm="1">
         <f t="array" ref="M421">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20605,11 +20674,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L422" s="37" t="str" cm="1">
+      <c r="L422" s="30" t="str" cm="1">
         <f t="array" ref="L422">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M422" s="39" t="str" cm="1">
+      <c r="M422" s="32" t="str" cm="1">
         <f t="array" ref="M422">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20649,11 +20718,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L423" s="37" t="str" cm="1">
+      <c r="L423" s="30" t="str" cm="1">
         <f t="array" ref="L423">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M423" s="39" t="str" cm="1">
+      <c r="M423" s="32" t="str" cm="1">
         <f t="array" ref="M423">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -20693,11 +20762,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L424" s="37" t="str" cm="1">
+      <c r="L424" s="30" t="str" cm="1">
         <f t="array" ref="L424">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M424" s="39" t="str" cm="1">
+      <c r="M424" s="32" t="str" cm="1">
         <f t="array" ref="M424">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -20737,11 +20806,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L425" s="37" t="str" cm="1">
+      <c r="L425" s="30" t="str" cm="1">
         <f t="array" ref="L425">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M425" s="39" t="str" cm="1">
+      <c r="M425" s="32" t="str" cm="1">
         <f t="array" ref="M425">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20781,11 +20850,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L426" s="37" t="str" cm="1">
+      <c r="L426" s="30" t="str" cm="1">
         <f t="array" ref="L426">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M426" s="39" t="str" cm="1">
+      <c r="M426" s="32" t="str" cm="1">
         <f t="array" ref="M426">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20825,11 +20894,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L427" s="37" t="str" cm="1">
+      <c r="L427" s="30" t="str" cm="1">
         <f t="array" ref="L427">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M427" s="39" t="str" cm="1">
+      <c r="M427" s="32" t="str" cm="1">
         <f t="array" ref="M427">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20869,11 +20938,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L428" s="37" t="str" cm="1">
+      <c r="L428" s="30" t="str" cm="1">
         <f t="array" ref="L428">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M428" s="39" t="str" cm="1">
+      <c r="M428" s="32" t="str" cm="1">
         <f t="array" ref="M428">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -20913,11 +20982,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L429" s="37" t="str" cm="1">
+      <c r="L429" s="30" t="str" cm="1">
         <f t="array" ref="L429">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M429" s="39" t="str" cm="1">
+      <c r="M429" s="32" t="str" cm="1">
         <f t="array" ref="M429">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -20957,11 +21026,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L430" s="37" t="str" cm="1">
+      <c r="L430" s="30" t="str" cm="1">
         <f t="array" ref="L430">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M430" s="39" t="str" cm="1">
+      <c r="M430" s="32" t="str" cm="1">
         <f t="array" ref="M430">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21001,11 +21070,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L431" s="37" t="str" cm="1">
+      <c r="L431" s="30" t="str" cm="1">
         <f t="array" ref="L431">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M431" s="39" t="str" cm="1">
+      <c r="M431" s="32" t="str" cm="1">
         <f t="array" ref="M431">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21045,11 +21114,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L432" s="37" t="str" cm="1">
+      <c r="L432" s="30" t="str" cm="1">
         <f t="array" ref="L432">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M432" s="39" t="str" cm="1">
+      <c r="M432" s="32" t="str" cm="1">
         <f t="array" ref="M432">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21089,11 +21158,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L433" s="37" t="str" cm="1">
+      <c r="L433" s="30" t="str" cm="1">
         <f t="array" ref="L433">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M433" s="39" t="str" cm="1">
+      <c r="M433" s="32" t="str" cm="1">
         <f t="array" ref="M433">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21133,11 +21202,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L434" s="37" t="str" cm="1">
+      <c r="L434" s="30" t="str" cm="1">
         <f t="array" ref="L434">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M434" s="39" t="str" cm="1">
+      <c r="M434" s="32" t="str" cm="1">
         <f t="array" ref="M434">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21177,11 +21246,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L435" s="37" t="str" cm="1">
+      <c r="L435" s="30" t="str" cm="1">
         <f t="array" ref="L435">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M435" s="39" t="str" cm="1">
+      <c r="M435" s="32" t="str" cm="1">
         <f t="array" ref="M435">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -21221,11 +21290,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L436" s="37" t="str" cm="1">
+      <c r="L436" s="30" t="str" cm="1">
         <f t="array" ref="L436">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M436" s="39" t="str" cm="1">
+      <c r="M436" s="32" t="str" cm="1">
         <f t="array" ref="M436">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -21265,11 +21334,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L437" s="37" t="str" cm="1">
+      <c r="L437" s="30" t="str" cm="1">
         <f t="array" ref="L437">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M437" s="39" t="str" cm="1">
+      <c r="M437" s="32" t="str" cm="1">
         <f t="array" ref="M437">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21309,11 +21378,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L438" s="37" t="str" cm="1">
+      <c r="L438" s="30" t="str" cm="1">
         <f t="array" ref="L438">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M438" s="39" t="str" cm="1">
+      <c r="M438" s="32" t="str" cm="1">
         <f t="array" ref="M438">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -21353,11 +21422,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L439" s="37" t="str" cm="1">
+      <c r="L439" s="30" t="str" cm="1">
         <f t="array" ref="L439">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M439" s="39" t="str" cm="1">
+      <c r="M439" s="32" t="str" cm="1">
         <f t="array" ref="M439">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21397,11 +21466,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L440" s="37" t="str" cm="1">
+      <c r="L440" s="30" t="str" cm="1">
         <f t="array" ref="L440">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M440" s="39" t="str" cm="1">
+      <c r="M440" s="32" t="str" cm="1">
         <f t="array" ref="M440">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21441,11 +21510,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L441" s="37" t="str" cm="1">
+      <c r="L441" s="30" t="str" cm="1">
         <f t="array" ref="L441">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M441" s="39" t="str" cm="1">
+      <c r="M441" s="32" t="str" cm="1">
         <f t="array" ref="M441">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21485,11 +21554,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L442" s="37" t="str" cm="1">
+      <c r="L442" s="30" t="str" cm="1">
         <f t="array" ref="L442">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M442" s="39" t="str" cm="1">
+      <c r="M442" s="32" t="str" cm="1">
         <f t="array" ref="M442">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21529,11 +21598,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L443" s="37" t="str" cm="1">
+      <c r="L443" s="30" t="str" cm="1">
         <f t="array" ref="L443">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M443" s="39" t="str" cm="1">
+      <c r="M443" s="32" t="str" cm="1">
         <f t="array" ref="M443">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -21573,11 +21642,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L444" s="37" t="str" cm="1">
+      <c r="L444" s="30" t="str" cm="1">
         <f t="array" ref="L444">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M444" s="39" t="str" cm="1">
+      <c r="M444" s="32" t="str" cm="1">
         <f t="array" ref="M444">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -21617,11 +21686,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L445" s="37" t="str" cm="1">
+      <c r="L445" s="30" t="str" cm="1">
         <f t="array" ref="L445">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M445" s="39" t="str" cm="1">
+      <c r="M445" s="32" t="str" cm="1">
         <f t="array" ref="M445">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21661,11 +21730,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L446" s="37" t="str" cm="1">
+      <c r="L446" s="30" t="str" cm="1">
         <f t="array" ref="L446">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M446" s="39" t="str" cm="1">
+      <c r="M446" s="32" t="str" cm="1">
         <f t="array" ref="M446">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -21705,11 +21774,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L447" s="37" t="str" cm="1">
+      <c r="L447" s="30" t="str" cm="1">
         <f t="array" ref="L447">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M447" s="39" t="str" cm="1">
+      <c r="M447" s="32" t="str" cm="1">
         <f t="array" ref="M447">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21749,11 +21818,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L448" s="37" t="str" cm="1">
+      <c r="L448" s="30" t="str" cm="1">
         <f t="array" ref="L448">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M448" s="39" t="str" cm="1">
+      <c r="M448" s="32" t="str" cm="1">
         <f t="array" ref="M448">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21793,11 +21862,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L449" s="37" t="str" cm="1">
+      <c r="L449" s="30" t="str" cm="1">
         <f t="array" ref="L449">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M449" s="39" t="str" cm="1">
+      <c r="M449" s="32" t="str" cm="1">
         <f t="array" ref="M449">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21837,11 +21906,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L450" s="37" t="str" cm="1">
+      <c r="L450" s="30" t="str" cm="1">
         <f t="array" ref="L450">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M450" s="39" t="str" cm="1">
+      <c r="M450" s="32" t="str" cm="1">
         <f t="array" ref="M450">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21881,11 +21950,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L451" s="37" t="str" cm="1">
+      <c r="L451" s="30" t="str" cm="1">
         <f t="array" ref="L451">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M451" s="39" t="str" cm="1">
+      <c r="M451" s="32" t="str" cm="1">
         <f t="array" ref="M451">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21925,11 +21994,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L452" s="37" t="str" cm="1">
+      <c r="L452" s="30" t="str" cm="1">
         <f t="array" ref="L452">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M452" s="39" t="str" cm="1">
+      <c r="M452" s="32" t="str" cm="1">
         <f t="array" ref="M452">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -21969,11 +22038,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L453" s="37" t="str" cm="1">
+      <c r="L453" s="30" t="str" cm="1">
         <f t="array" ref="L453">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M453" s="39" t="str" cm="1">
+      <c r="M453" s="32" t="str" cm="1">
         <f t="array" ref="M453">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22013,11 +22082,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L454" s="37" t="str" cm="1">
+      <c r="L454" s="30" t="str" cm="1">
         <f t="array" ref="L454">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M454" s="39" t="str" cm="1">
+      <c r="M454" s="32" t="str" cm="1">
         <f t="array" ref="M454">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22057,11 +22126,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L455" s="37" t="str" cm="1">
+      <c r="L455" s="30" t="str" cm="1">
         <f t="array" ref="L455">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M455" s="39" t="str" cm="1">
+      <c r="M455" s="32" t="str" cm="1">
         <f t="array" ref="M455">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22101,11 +22170,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L456" s="37" t="str" cm="1">
+      <c r="L456" s="30" t="str" cm="1">
         <f t="array" ref="L456">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M456" s="39" t="str" cm="1">
+      <c r="M456" s="32" t="str" cm="1">
         <f t="array" ref="M456">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22145,11 +22214,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L457" s="37" t="str" cm="1">
+      <c r="L457" s="30" t="str" cm="1">
         <f t="array" ref="L457">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M457" s="39" t="str" cm="1">
+      <c r="M457" s="32" t="str" cm="1">
         <f t="array" ref="M457">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22189,11 +22258,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L458" s="37" t="str" cm="1">
+      <c r="L458" s="30" t="str" cm="1">
         <f t="array" ref="L458">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M458" s="39" t="str" cm="1">
+      <c r="M458" s="32" t="str" cm="1">
         <f t="array" ref="M458">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22233,11 +22302,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L459" s="37" t="str" cm="1">
+      <c r="L459" s="30" t="str" cm="1">
         <f t="array" ref="L459">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M459" s="39" t="str" cm="1">
+      <c r="M459" s="32" t="str" cm="1">
         <f t="array" ref="M459">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22277,11 +22346,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L460" s="37" t="str" cm="1">
+      <c r="L460" s="30" t="str" cm="1">
         <f t="array" ref="L460">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M460" s="39" t="str" cm="1">
+      <c r="M460" s="32" t="str" cm="1">
         <f t="array" ref="M460">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22321,11 +22390,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L461" s="37" t="str" cm="1">
+      <c r="L461" s="30" t="str" cm="1">
         <f t="array" ref="L461">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M461" s="39" t="str" cm="1">
+      <c r="M461" s="32" t="str" cm="1">
         <f t="array" ref="M461">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -22365,11 +22434,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L462" s="37" t="str" cm="1">
+      <c r="L462" s="30" t="str" cm="1">
         <f t="array" ref="L462">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M462" s="39" t="str" cm="1">
+      <c r="M462" s="32" t="str" cm="1">
         <f t="array" ref="M462">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22409,11 +22478,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L463" s="37" t="str" cm="1">
+      <c r="L463" s="30" t="str" cm="1">
         <f t="array" ref="L463">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M463" s="39" t="str" cm="1">
+      <c r="M463" s="32" t="str" cm="1">
         <f t="array" ref="M463">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22453,11 +22522,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L464" s="37" t="str" cm="1">
+      <c r="L464" s="30" t="str" cm="1">
         <f t="array" ref="L464">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M464" s="39" t="str" cm="1">
+      <c r="M464" s="32" t="str" cm="1">
         <f t="array" ref="M464">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -22497,11 +22566,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L465" s="37" t="str" cm="1">
+      <c r="L465" s="30" t="str" cm="1">
         <f t="array" ref="L465">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M465" s="39" t="str" cm="1">
+      <c r="M465" s="32" t="str" cm="1">
         <f t="array" ref="M465">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22541,11 +22610,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L466" s="37" t="str" cm="1">
+      <c r="L466" s="30" t="str" cm="1">
         <f t="array" ref="L466">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M466" s="39" t="str" cm="1">
+      <c r="M466" s="32" t="str" cm="1">
         <f t="array" ref="M466">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22585,11 +22654,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L467" s="37" t="str" cm="1">
+      <c r="L467" s="30" t="str" cm="1">
         <f t="array" ref="L467">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M467" s="39" t="str" cm="1">
+      <c r="M467" s="32" t="str" cm="1">
         <f t="array" ref="M467">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22629,11 +22698,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L468" s="37" t="str" cm="1">
+      <c r="L468" s="30" t="str" cm="1">
         <f t="array" ref="L468">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M468" s="39" t="str" cm="1">
+      <c r="M468" s="32" t="str" cm="1">
         <f t="array" ref="M468">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22673,11 +22742,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L469" s="37" t="str" cm="1">
+      <c r="L469" s="30" t="str" cm="1">
         <f t="array" ref="L469">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M469" s="39" t="str" cm="1">
+      <c r="M469" s="32" t="str" cm="1">
         <f t="array" ref="M469">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22717,11 +22786,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L470" s="37" t="str" cm="1">
+      <c r="L470" s="30" t="str" cm="1">
         <f t="array" ref="L470">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M470" s="39" t="str" cm="1">
+      <c r="M470" s="32" t="str" cm="1">
         <f t="array" ref="M470">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22761,11 +22830,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L471" s="37" t="str" cm="1">
+      <c r="L471" s="30" t="str" cm="1">
         <f t="array" ref="L471">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M471" s="39" t="str" cm="1">
+      <c r="M471" s="32" t="str" cm="1">
         <f t="array" ref="M471">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22805,11 +22874,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L472" s="37" t="str" cm="1">
+      <c r="L472" s="30" t="str" cm="1">
         <f t="array" ref="L472">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M472" s="39" t="str" cm="1">
+      <c r="M472" s="32" t="str" cm="1">
         <f t="array" ref="M472">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22849,11 +22918,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L473" s="37" t="str" cm="1">
+      <c r="L473" s="30" t="str" cm="1">
         <f t="array" ref="L473">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M473" s="39" t="str" cm="1">
+      <c r="M473" s="32" t="str" cm="1">
         <f t="array" ref="M473">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22893,11 +22962,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L474" s="37" t="str" cm="1">
+      <c r="L474" s="30" t="str" cm="1">
         <f t="array" ref="L474">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M474" s="39" t="str" cm="1">
+      <c r="M474" s="32" t="str" cm="1">
         <f t="array" ref="M474">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22937,11 +23006,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L475" s="37" t="str" cm="1">
+      <c r="L475" s="30" t="str" cm="1">
         <f t="array" ref="L475">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M475" s="39" t="str" cm="1">
+      <c r="M475" s="32" t="str" cm="1">
         <f t="array" ref="M475">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -22981,11 +23050,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L476" s="37" t="str" cm="1">
+      <c r="L476" s="30" t="str" cm="1">
         <f t="array" ref="L476">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M476" s="39" t="str" cm="1">
+      <c r="M476" s="32" t="str" cm="1">
         <f t="array" ref="M476">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23025,11 +23094,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L477" s="37" t="str" cm="1">
+      <c r="L477" s="30" t="str" cm="1">
         <f t="array" ref="L477">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M477" s="39" t="str" cm="1">
+      <c r="M477" s="32" t="str" cm="1">
         <f t="array" ref="M477">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23069,11 +23138,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L478" s="37" t="str" cm="1">
+      <c r="L478" s="30" t="str" cm="1">
         <f t="array" ref="L478">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M478" s="39" t="str" cm="1">
+      <c r="M478" s="32" t="str" cm="1">
         <f t="array" ref="M478">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23113,11 +23182,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L479" s="37" t="str" cm="1">
+      <c r="L479" s="30" t="str" cm="1">
         <f t="array" ref="L479">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M479" s="39" t="str" cm="1">
+      <c r="M479" s="32" t="str" cm="1">
         <f t="array" ref="M479">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23157,11 +23226,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L480" s="37" t="str" cm="1">
+      <c r="L480" s="30" t="str" cm="1">
         <f t="array" ref="L480">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M480" s="39" t="str" cm="1">
+      <c r="M480" s="32" t="str" cm="1">
         <f t="array" ref="M480">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -23201,11 +23270,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L481" s="37" t="str" cm="1">
+      <c r="L481" s="30" t="str" cm="1">
         <f t="array" ref="L481">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M481" s="39" t="str" cm="1">
+      <c r="M481" s="32" t="str" cm="1">
         <f t="array" ref="M481">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23245,11 +23314,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L482" s="37" t="str" cm="1">
+      <c r="L482" s="30" t="str" cm="1">
         <f t="array" ref="L482">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M482" s="39" t="str" cm="1">
+      <c r="M482" s="32" t="str" cm="1">
         <f t="array" ref="M482">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -23289,11 +23358,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L483" s="37" t="str" cm="1">
+      <c r="L483" s="30" t="str" cm="1">
         <f t="array" ref="L483">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M483" s="39" t="str" cm="1">
+      <c r="M483" s="32" t="str" cm="1">
         <f t="array" ref="M483">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23333,11 +23402,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L484" s="37" t="str" cm="1">
+      <c r="L484" s="30" t="str" cm="1">
         <f t="array" ref="L484">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M484" s="39" t="str" cm="1">
+      <c r="M484" s="32" t="str" cm="1">
         <f t="array" ref="M484">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23377,11 +23446,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L485" s="37" t="str" cm="1">
+      <c r="L485" s="30" t="str" cm="1">
         <f t="array" ref="L485">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M485" s="39" t="str" cm="1">
+      <c r="M485" s="32" t="str" cm="1">
         <f t="array" ref="M485">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -23421,11 +23490,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L486" s="37" t="str" cm="1">
+      <c r="L486" s="30" t="str" cm="1">
         <f t="array" ref="L486">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M486" s="39" t="str" cm="1">
+      <c r="M486" s="32" t="str" cm="1">
         <f t="array" ref="M486">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23465,11 +23534,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L487" s="37" t="str" cm="1">
+      <c r="L487" s="30" t="str" cm="1">
         <f t="array" ref="L487">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M487" s="39" t="str" cm="1">
+      <c r="M487" s="32" t="str" cm="1">
         <f t="array" ref="M487">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23509,11 +23578,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L488" s="37" t="str" cm="1">
+      <c r="L488" s="30" t="str" cm="1">
         <f t="array" ref="L488">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M488" s="39" t="str" cm="1">
+      <c r="M488" s="32" t="str" cm="1">
         <f t="array" ref="M488">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -23553,11 +23622,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L489" s="37" t="str" cm="1">
+      <c r="L489" s="30" t="str" cm="1">
         <f t="array" ref="L489">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M489" s="39" t="str" cm="1">
+      <c r="M489" s="32" t="str" cm="1">
         <f t="array" ref="M489">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23597,11 +23666,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L490" s="37" t="str" cm="1">
+      <c r="L490" s="30" t="str" cm="1">
         <f t="array" ref="L490">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M490" s="39" t="str" cm="1">
+      <c r="M490" s="32" t="str" cm="1">
         <f t="array" ref="M490">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23641,11 +23710,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L491" s="37" t="str" cm="1">
+      <c r="L491" s="30" t="str" cm="1">
         <f t="array" ref="L491">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M491" s="39" t="str" cm="1">
+      <c r="M491" s="32" t="str" cm="1">
         <f t="array" ref="M491">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23685,11 +23754,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L492" s="37" t="str" cm="1">
+      <c r="L492" s="30" t="str" cm="1">
         <f t="array" ref="L492">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M492" s="39" t="str" cm="1">
+      <c r="M492" s="32" t="str" cm="1">
         <f t="array" ref="M492">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -23729,11 +23798,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L493" s="37" t="str" cm="1">
+      <c r="L493" s="30" t="str" cm="1">
         <f t="array" ref="L493">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M493" s="39" t="str" cm="1">
+      <c r="M493" s="32" t="str" cm="1">
         <f t="array" ref="M493">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -23773,11 +23842,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L494" s="37" t="str" cm="1">
+      <c r="L494" s="30" t="str" cm="1">
         <f t="array" ref="L494">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M494" s="39" t="str" cm="1">
+      <c r="M494" s="32" t="str" cm="1">
         <f t="array" ref="M494">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -23817,11 +23886,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L495" s="37" t="str" cm="1">
+      <c r="L495" s="30" t="str" cm="1">
         <f t="array" ref="L495">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M495" s="39" t="str" cm="1">
+      <c r="M495" s="32" t="str" cm="1">
         <f t="array" ref="M495">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Average</v>
       </c>
@@ -23861,11 +23930,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L496" s="37" t="str" cm="1">
+      <c r="L496" s="30" t="str" cm="1">
         <f t="array" ref="L496">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M496" s="39" t="str" cm="1">
+      <c r="M496" s="32" t="str" cm="1">
         <f t="array" ref="M496">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23905,11 +23974,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L497" s="37" t="str" cm="1">
+      <c r="L497" s="30" t="str" cm="1">
         <f t="array" ref="L497">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M497" s="39" t="str" cm="1">
+      <c r="M497" s="32" t="str" cm="1">
         <f t="array" ref="M497">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23949,11 +24018,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L498" s="37" t="str" cm="1">
+      <c r="L498" s="30" t="str" cm="1">
         <f t="array" ref="L498">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Poor Sale</v>
       </c>
-      <c r="M498" s="39" t="str" cm="1">
+      <c r="M498" s="32" t="str" cm="1">
         <f t="array" ref="M498">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -23993,11 +24062,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L499" s="37" t="str" cm="1">
+      <c r="L499" s="30" t="str" cm="1">
         <f t="array" ref="L499">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M499" s="39" t="str" cm="1">
+      <c r="M499" s="32" t="str" cm="1">
         <f t="array" ref="M499">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -24037,11 +24106,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>BEST SALE</v>
       </c>
-      <c r="L500" s="37" t="str" cm="1">
+      <c r="L500" s="30" t="str" cm="1">
         <f t="array" ref="L500">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Best Sale</v>
       </c>
-      <c r="M500" s="39" t="str" cm="1">
+      <c r="M500" s="32" t="str" cm="1">
         <f t="array" ref="M500">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Best</v>
       </c>
@@ -24081,11 +24150,11 @@
         <f>IF(Table4[[#This Row],[Sales]]&gt;=40000,"BEST SALE","POOR SALE")</f>
         <v>POOR SALE</v>
       </c>
-      <c r="L501" s="37" t="str" cm="1">
+      <c r="L501" s="30" t="str" cm="1">
         <f t="array" ref="L501">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best Sale", Table4[[#This Row],[Sales]]&gt;=20000,"Average Sale",Table4[[#This Row],[Sales]]&gt;0,"Poor Sale")</f>
         <v>Average Sale</v>
       </c>
-      <c r="M501" s="39" t="str" cm="1">
+      <c r="M501" s="32" t="str" cm="1">
         <f t="array" ref="M501">_xlfn.IFS(Table4[[#This Row],[Sales]]&gt;=40000,"Best", Table4[[#This Row],[Sales]]&gt;=35000,"Average",Table4[[#This Row],[Sales]]&gt;0,"Poor")</f>
         <v>Poor</v>
       </c>
@@ -24099,6 +24168,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="P21:U21"/>
+    <mergeCell ref="N37:W37"/>
+    <mergeCell ref="N38:W38"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="N35:W35"/>
+    <mergeCell ref="N36:W36"/>
+    <mergeCell ref="N30:W30"/>
+    <mergeCell ref="N31:W31"/>
+    <mergeCell ref="N32:W32"/>
+    <mergeCell ref="N33:W33"/>
+    <mergeCell ref="N34:W34"/>
+    <mergeCell ref="Z36:AA36"/>
     <mergeCell ref="AB36:AC36"/>
     <mergeCell ref="W13:Z13"/>
     <mergeCell ref="W12:Z12"/>
@@ -24115,19 +24197,6 @@
     <mergeCell ref="N16:S16"/>
     <mergeCell ref="N17:S17"/>
     <mergeCell ref="N18:S18"/>
-    <mergeCell ref="P21:U21"/>
-    <mergeCell ref="N37:W37"/>
-    <mergeCell ref="N38:W38"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="N35:W35"/>
-    <mergeCell ref="N36:W36"/>
-    <mergeCell ref="N30:W30"/>
-    <mergeCell ref="N31:W31"/>
-    <mergeCell ref="N32:W32"/>
-    <mergeCell ref="N33:W33"/>
-    <mergeCell ref="N34:W34"/>
-    <mergeCell ref="Z36:AA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
